--- a/trackers/LCrev.xlsx
+++ b/trackers/LCrev.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="969">
   <si>
     <t xml:space="preserve">DSA-Notes</t>
   </si>
@@ -150,6 +150,15 @@
   </si>
   <si>
     <t xml:space="preserve">Prefix into `res`, suffix as scalar → multiply and move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valid-sudoku/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hashset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hashset for each row,col, box, if duplicate return false</t>
   </si>
   <si>
     <t xml:space="preserve">Problem </t>
@@ -4323,28 +4332,70 @@
       <c r="G9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="26"/>
+      <c r="H9" s="13" t="n">
+        <f aca="false">D9+2</f>
+        <v>45886</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <f aca="false">D9+7</f>
+        <v>45891</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <f aca="false">D9+21</f>
+        <v>45905</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <f aca="false">D9+45</f>
+        <v>45929</v>
+      </c>
+      <c r="L9" s="18" t="n">
+        <f aca="false">D9+60</f>
+        <v>45944</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="n">
         <f aca="false">ROW()-2</f>
         <v>8</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="26"/>
+      <c r="B10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <f aca="false">D10+2</f>
+        <v>45886</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <f aca="false">D10+7</f>
+        <v>45891</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <f aca="false">D10+21</f>
+        <v>45905</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <f aca="false">D10+45</f>
+        <v>45929</v>
+      </c>
+      <c r="L10" s="18" t="n">
+        <f aca="false">D10+60</f>
+        <v>45944</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="n">
@@ -8469,6 +8520,7 @@
     <hyperlink ref="B7" r:id="rId6" display="347. Top K Frequent Elements"/>
     <hyperlink ref="B8" r:id="rId7" display="Group Anagrams"/>
     <hyperlink ref="B9" r:id="rId8" display="product-of-array-except-self"/>
+    <hyperlink ref="B10" r:id="rId9" display="valid-sudoku/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -8494,167 +8546,167 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="73" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="73" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="73" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="73" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="73" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="73" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="73" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="73" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="73" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="73" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="73" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="73" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="73" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="73" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="73" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="73" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="73" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="73" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="73" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="73" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="73" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="73" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="73" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="73" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="73" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="73" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="73" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="73" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="73" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="73" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="73" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="73" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="73" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
   </sheetData>
@@ -8750,94 +8802,94 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="74" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B1" s="75" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C1" s="75" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D2" s="76" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D3" s="76" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C4" s="77" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D4" s="76" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C5" s="77" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8846,40 +8898,40 @@
     </row>
     <row r="13" customFormat="false" ht="35.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="79" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B13" s="79"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8888,211 +8940,211 @@
     </row>
     <row r="19" customFormat="false" ht="19.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="79" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B19" s="79"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="80" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B20" s="80"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="80" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B21" s="80"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="80" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B22" s="80"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="80" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B23" s="80"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C26" s="46" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="81" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="81" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B28" s="24" t="s">
+        <v>923</v>
+      </c>
+      <c r="C28" s="24" t="s">
         <v>920</v>
       </c>
-      <c r="C28" s="24" t="s">
-        <v>917</v>
-      </c>
       <c r="D28" s="24" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="46" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B35" s="46" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="81" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="81" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="81" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="81" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="81" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="81" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="81" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="81" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="81" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="81" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="24" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="24" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
   </sheetData>
@@ -9137,7 +9189,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9146,10 +9198,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9158,10 +9210,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9170,10 +9222,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9182,10 +9234,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9194,10 +9246,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9206,10 +9258,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9218,10 +9270,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9230,10 +9282,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9242,7 +9294,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="60" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="C10" s="43"/>
     </row>
@@ -9252,7 +9304,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C11" s="43"/>
     </row>
@@ -9262,7 +9314,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C12" s="43"/>
     </row>
@@ -9272,7 +9324,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C13" s="43"/>
     </row>
@@ -9511,12 +9563,12 @@
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="82" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
   </sheetData>
@@ -9548,10 +9600,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>3</v>
@@ -9563,10 +9615,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>14</v>
@@ -9581,7 +9633,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>14</v>
@@ -9596,7 +9648,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>14</v>
@@ -9611,7 +9663,7 @@
         <v>28</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>29</v>
@@ -9626,7 +9678,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>14</v>
@@ -12344,36 +12396,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B2" s="33" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12382,13 +12434,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12397,13 +12449,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12412,13 +12464,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12427,13 +12479,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12442,13 +12494,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12457,13 +12509,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12471,19 +12523,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B10" s="33" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12492,13 +12544,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12507,13 +12559,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12522,13 +12574,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12537,13 +12589,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12552,13 +12604,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12567,13 +12619,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12581,19 +12633,19 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B18" s="33" t="n">
         <v>15</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12602,13 +12654,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12617,13 +12669,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12632,13 +12684,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12647,13 +12699,13 @@
         <v>19</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12662,13 +12714,13 @@
         <v>20</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12677,13 +12729,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12691,19 +12743,19 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B26" s="33" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12712,13 +12764,13 @@
         <v>23</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12727,13 +12779,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12742,13 +12794,13 @@
         <v>25</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12757,13 +12809,13 @@
         <v>26</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12772,13 +12824,13 @@
         <v>27</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12787,13 +12839,13 @@
         <v>28</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12802,13 +12854,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12817,13 +12869,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -12858,7 +12910,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="36" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="36"/>
@@ -12871,13 +12923,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="37" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -12888,13 +12940,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -12905,13 +12957,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -12922,13 +12974,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -12939,13 +12991,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -12956,13 +13008,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -12973,13 +13025,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -12990,13 +13042,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -13007,13 +13059,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -13024,13 +13076,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -13041,13 +13093,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -13058,13 +13110,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -13075,13 +13127,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -13092,13 +13144,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -13109,13 +13161,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -13126,13 +13178,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -13143,13 +13195,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -13160,13 +13212,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -13177,13 +13229,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -13194,13 +13246,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -13211,13 +13263,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -13228,13 +13280,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -13294,22 +13346,22 @@
         <v>4</v>
       </c>
       <c r="D29" s="37" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13318,7 +13370,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>45729</v>
@@ -13354,7 +13406,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>45729</v>
@@ -13390,7 +13442,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>45729</v>
@@ -13426,7 +13478,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>45729</v>
@@ -13462,7 +13514,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C34" s="25" t="n">
         <v>45729</v>
@@ -13498,7 +13550,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C35" s="25" t="n">
         <v>45729</v>
@@ -13534,7 +13586,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C36" s="25" t="n">
         <v>45729</v>
@@ -13570,7 +13622,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C37" s="25" t="n">
         <v>45729</v>
@@ -13606,7 +13658,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C38" s="25" t="n">
         <v>45729</v>
@@ -13642,7 +13694,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C39" s="25" t="n">
         <v>45729</v>
@@ -13678,7 +13730,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C40" s="25" t="n">
         <v>45729</v>
@@ -13714,7 +13766,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="40" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C41" s="25" t="n">
         <v>45729</v>
@@ -13750,7 +13802,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="40" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C42" s="25" t="n">
         <v>45729</v>
@@ -13786,7 +13838,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="41" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C43" s="25" t="n">
         <v>45729</v>
@@ -13822,7 +13874,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="41" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C44" s="25" t="n">
         <v>45729</v>
@@ -13858,7 +13910,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="41" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C45" s="25" t="n">
         <v>45729</v>
@@ -13894,7 +13946,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="41" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C46" s="25" t="n">
         <v>45729</v>
@@ -13930,7 +13982,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="41" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C47" s="25" t="n">
         <v>45729</v>
@@ -13966,7 +14018,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="41" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C48" s="25" t="n">
         <v>45729</v>
@@ -14002,7 +14054,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="41" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C49" s="25" t="n">
         <v>45729</v>
@@ -14038,7 +14090,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="41" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C50" s="25" t="n">
         <v>45729</v>
@@ -14074,7 +14126,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="41" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C51" s="25" t="n">
         <v>45729</v>
@@ -14110,7 +14162,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="41" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C52" s="25" t="n">
         <v>45729</v>
@@ -14146,7 +14198,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="41" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C53" s="25" t="n">
         <v>45729</v>
@@ -14422,7 +14474,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q1" s="44" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="R1" s="44"/>
       <c r="S1" s="44"/>
@@ -14430,119 +14482,119 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q2" s="31" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R2" s="31" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S2" s="31" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="T2" s="31" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q3" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q4" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q6" s="15" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S6" s="15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="T6" s="15" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q7" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="S7" s="15" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q8" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q9" s="15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="S9" s="15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q12" s="45" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="R12" s="45"/>
       <c r="S12" s="45"/>
@@ -14550,119 +14602,119 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q13" s="46" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R13" s="46" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S13" s="46" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="T13" s="46" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q14" s="24" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q15" s="24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="T15" s="24" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q16" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="T16" s="24" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q17" s="24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="T17" s="24" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q18" s="24" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="T18" s="24" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q19" s="24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="R19" s="24" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T19" s="24" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q20" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="R20" s="24" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T20" s="24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q23" s="45" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="R23" s="45"/>
       <c r="S23" s="45"/>
@@ -14670,119 +14722,119 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q24" s="46" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R24" s="46" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S24" s="46" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="T24" s="46" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q25" s="24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R25" s="24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="S25" s="24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="T25" s="24" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q26" s="24" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="S26" s="24" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="T26" s="24" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q27" s="24" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="R27" s="24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="S27" s="24" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="T27" s="24" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q28" s="24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="S28" s="24" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="T28" s="24" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q29" s="24" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="T29" s="24" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q30" s="24" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="R30" s="24" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="S30" s="24" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="T30" s="24" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q31" s="24" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R31" s="24" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="S31" s="24" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="T31" s="24" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q33" s="45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="R33" s="45"/>
       <c r="S33" s="45"/>
@@ -14790,154 +14842,154 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q34" s="46" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R34" s="46" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S34" s="46" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="T34" s="46" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q35" s="24" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="R35" s="24" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="S35" s="24" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="T35" s="24" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q36" s="24" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="R36" s="24" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="S36" s="24" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="T36" s="24" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q37" s="24" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="R37" s="24" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="S37" s="24" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="T37" s="24" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q38" s="24" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="R38" s="24" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="S38" s="24" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T38" s="24" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q39" s="24" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="R39" s="24" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="S39" s="24" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="T39" s="24" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q40" s="24" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="R40" s="24" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="S40" s="24" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="T40" s="24" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q41" s="24" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="R41" s="24" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="S41" s="24" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="T41" s="24" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q44" s="47" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="R44" s="47"/>
       <c r="S44" s="47"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q45" s="46" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R45" s="46" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="S45" s="46" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q46" s="24" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="R46" s="24" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="S46" s="24" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q47" s="24" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="R47" s="24" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="S47" s="24" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -14974,291 +15026,291 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="48" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B1" s="48" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C1" s="48" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="49" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="49" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="49" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="49" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="49" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="49" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="49" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B13" s="49" t="s">
+        <v>379</v>
+      </c>
+      <c r="C13" s="49" t="s">
         <v>376</v>
       </c>
-      <c r="C13" s="49" t="s">
-        <v>373</v>
-      </c>
       <c r="D13" s="49" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="50" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C23" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C24" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C26" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -15292,13 +15344,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -15310,13 +15362,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E2" s="52" t="s">
         <v>14</v>
@@ -15328,13 +15380,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D3" s="51" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E3" s="52" t="s">
         <v>14</v>
@@ -15346,13 +15398,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E4" s="52" t="s">
         <v>29</v>
@@ -15364,13 +15416,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E5" s="52" t="s">
         <v>14</v>
@@ -15382,13 +15434,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E6" s="52" t="s">
         <v>29</v>
@@ -15400,13 +15452,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E7" s="52" t="s">
         <v>29</v>
@@ -15418,13 +15470,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E8" s="52" t="s">
         <v>29</v>
@@ -15436,13 +15488,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E9" s="52" t="s">
         <v>29</v>
@@ -15454,13 +15506,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E10" s="52" t="s">
         <v>14</v>
@@ -15472,13 +15524,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E11" s="52" t="s">
         <v>29</v>
@@ -15490,13 +15542,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E12" s="52" t="s">
         <v>29</v>
@@ -15508,13 +15560,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E13" s="52" t="s">
         <v>29</v>
@@ -15526,13 +15578,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E14" s="52" t="s">
         <v>14</v>
@@ -15544,13 +15596,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E15" s="52" t="s">
         <v>14</v>
@@ -15562,13 +15614,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E16" s="52" t="s">
         <v>14</v>
@@ -15580,13 +15632,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E17" s="52" t="s">
         <v>14</v>
@@ -15598,13 +15650,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D18" s="51" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E18" s="52" t="s">
         <v>14</v>
@@ -15616,13 +15668,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E19" s="52" t="s">
         <v>29</v>
@@ -15634,13 +15686,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E20" s="52" t="s">
         <v>14</v>
@@ -15652,13 +15704,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E21" s="52" t="s">
         <v>29</v>
@@ -15670,13 +15722,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E22" s="52" t="s">
         <v>29</v>
@@ -15688,13 +15740,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E23" s="52" t="s">
         <v>29</v>
@@ -15706,13 +15758,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E24" s="52" t="s">
         <v>14</v>
@@ -15724,13 +15776,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E25" s="52" t="s">
         <v>14</v>
@@ -15742,13 +15794,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E26" s="52" t="s">
         <v>29</v>
@@ -15760,13 +15812,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E27" s="52" t="s">
         <v>14</v>
@@ -15778,16 +15830,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E28" s="52" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15796,16 +15848,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D29" s="51" t="s">
+        <v>473</v>
+      </c>
+      <c r="E29" s="52" t="s">
         <v>470</v>
-      </c>
-      <c r="E29" s="52" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15814,13 +15866,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E30" s="52" t="s">
         <v>29</v>
@@ -15832,13 +15884,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E31" s="52" t="s">
         <v>29</v>
@@ -15850,13 +15902,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E32" s="52" t="s">
         <v>29</v>
@@ -15868,13 +15920,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="51" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C33" s="51" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E33" s="52" t="s">
         <v>29</v>
@@ -15886,13 +15938,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E34" s="52" t="s">
         <v>29</v>
@@ -15904,13 +15956,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E35" s="52" t="s">
         <v>14</v>
@@ -15922,13 +15974,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E36" s="52" t="s">
         <v>29</v>
@@ -15940,13 +15992,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E37" s="52" t="s">
         <v>29</v>
@@ -15958,13 +16010,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C38" s="51" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D38" s="51" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E38" s="52" t="s">
         <v>29</v>
@@ -15976,13 +16028,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E39" s="52" t="s">
         <v>29</v>
@@ -15994,13 +16046,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C40" s="51" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E40" s="52" t="s">
         <v>29</v>
@@ -16012,13 +16064,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C41" s="51" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E41" s="52" t="s">
         <v>29</v>
@@ -16030,13 +16082,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D42" s="51" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E42" s="52" t="s">
         <v>29</v>
@@ -16048,16 +16100,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E43" s="52" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16066,13 +16118,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D44" s="51" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E44" s="52" t="s">
         <v>14</v>
@@ -16084,13 +16136,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C45" s="51" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E45" s="52" t="s">
         <v>14</v>
@@ -16102,13 +16154,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D46" s="51" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E46" s="52" t="s">
         <v>14</v>
@@ -16120,13 +16172,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D47" s="51" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E47" s="52" t="s">
         <v>29</v>
@@ -16138,13 +16190,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D48" s="51" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E48" s="52" t="s">
         <v>29</v>
@@ -16156,13 +16208,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E49" s="52" t="s">
         <v>29</v>
@@ -16171,13 +16223,13 @@
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>3</v>
@@ -16189,13 +16241,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>14</v>
@@ -16207,13 +16259,13 @@
         <v>2</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>14</v>
@@ -16225,13 +16277,13 @@
         <v>3</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>29</v>
@@ -16243,13 +16295,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>14</v>
@@ -16261,13 +16313,13 @@
         <v>5</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>29</v>
@@ -16279,13 +16331,13 @@
         <v>6</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>29</v>
@@ -16297,13 +16349,13 @@
         <v>7</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>29</v>
@@ -16315,13 +16367,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>14</v>
@@ -16333,13 +16385,13 @@
         <v>9</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>29</v>
@@ -16351,13 +16403,13 @@
         <v>10</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>29</v>
@@ -16369,13 +16421,13 @@
         <v>11</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>14</v>
@@ -16387,13 +16439,13 @@
         <v>12</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>14</v>
@@ -16405,13 +16457,13 @@
         <v>13</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>14</v>
@@ -16423,13 +16475,13 @@
         <v>14</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>14</v>
@@ -16441,13 +16493,13 @@
         <v>15</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>29</v>
@@ -16459,13 +16511,13 @@
         <v>16</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>14</v>
@@ -16477,13 +16529,13 @@
         <v>17</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>29</v>
@@ -16495,13 +16547,13 @@
         <v>18</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>29</v>
@@ -16513,13 +16565,13 @@
         <v>19</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>29</v>
@@ -16531,13 +16583,13 @@
         <v>20</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>14</v>
@@ -16549,13 +16601,13 @@
         <v>21</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>14</v>
@@ -16567,13 +16619,13 @@
         <v>22</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>14</v>
@@ -16585,13 +16637,13 @@
         <v>23</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>29</v>
@@ -16603,13 +16655,13 @@
         <v>24</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>14</v>
@@ -16621,16 +16673,16 @@
         <v>25</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16639,16 +16691,16 @@
         <v>26</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D77" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="E77" s="8" t="s">
         <v>470</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16657,13 +16709,13 @@
         <v>27</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>29</v>
@@ -16675,13 +16727,13 @@
         <v>28</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>29</v>
@@ -16693,13 +16745,13 @@
         <v>29</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>29</v>
@@ -16711,13 +16763,13 @@
         <v>30</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>29</v>
@@ -16729,13 +16781,13 @@
         <v>31</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>29</v>
@@ -16747,13 +16799,13 @@
         <v>32</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>29</v>
@@ -16765,16 +16817,16 @@
         <v>33</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16783,13 +16835,13 @@
         <v>34</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>29</v>
@@ -16801,13 +16853,13 @@
         <v>35</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>14</v>
@@ -16819,13 +16871,13 @@
         <v>36</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>29</v>
@@ -16837,13 +16889,13 @@
         <v>37</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>29</v>
@@ -16855,13 +16907,13 @@
         <v>38</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>29</v>
@@ -16873,13 +16925,13 @@
         <v>39</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>29</v>
@@ -16891,13 +16943,13 @@
         <v>40</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>29</v>
@@ -16909,13 +16961,13 @@
         <v>41</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>29</v>
@@ -16927,13 +16979,13 @@
         <v>42</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>29</v>
@@ -16945,13 +16997,13 @@
         <v>43</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>29</v>
@@ -16963,13 +17015,13 @@
         <v>44</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>29</v>
@@ -16981,16 +17033,16 @@
         <v>45</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>29</v>
@@ -17002,16 +17054,16 @@
         <v>46</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>29</v>
@@ -17023,16 +17075,16 @@
         <v>47</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>29</v>
@@ -17044,19 +17096,19 @@
         <v>48</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17065,16 +17117,16 @@
         <v>49</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>14</v>
@@ -17086,16 +17138,16 @@
         <v>50</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>14</v>
@@ -17106,22 +17158,22 @@
         <v>1</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="H106" s="9"/>
     </row>
@@ -17131,22 +17183,22 @@
         <v>1</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17155,19 +17207,19 @@
         <v>2</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17176,19 +17228,19 @@
         <v>3</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17197,19 +17249,19 @@
         <v>4</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17218,22 +17270,22 @@
         <v>5</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17242,22 +17294,22 @@
         <v>6</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17266,19 +17318,19 @@
         <v>7</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17287,22 +17339,22 @@
         <v>8</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17311,19 +17363,19 @@
         <v>9</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17332,19 +17384,19 @@
         <v>10</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17353,22 +17405,22 @@
         <v>11</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17377,19 +17429,19 @@
         <v>12</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17398,19 +17450,19 @@
         <v>13</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17419,22 +17471,22 @@
         <v>14</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17443,19 +17495,19 @@
         <v>15</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17464,19 +17516,19 @@
         <v>16</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17485,22 +17537,22 @@
         <v>17</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17509,19 +17561,19 @@
         <v>18</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17530,19 +17582,19 @@
         <v>19</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17551,28 +17603,28 @@
         <v>20</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17581,19 +17633,19 @@
         <v>21</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17602,19 +17654,19 @@
         <v>22</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17623,25 +17675,25 @@
         <v>23</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>14</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17650,19 +17702,19 @@
         <v>24</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17671,19 +17723,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17692,22 +17744,22 @@
         <v>26</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17716,19 +17768,19 @@
         <v>27</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17737,19 +17789,19 @@
         <v>28</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17758,22 +17810,22 @@
         <v>29</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17782,19 +17834,19 @@
         <v>30</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17803,19 +17855,19 @@
         <v>31</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17824,19 +17876,19 @@
         <v>32</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17845,28 +17897,28 @@
         <v>33</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>29</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17875,19 +17927,19 @@
         <v>34</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17896,19 +17948,19 @@
         <v>35</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17917,25 +17969,25 @@
         <v>36</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17944,19 +17996,19 @@
         <v>37</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17965,19 +18017,19 @@
         <v>38</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17986,31 +18038,31 @@
         <v>39</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18019,19 +18071,19 @@
         <v>40</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18040,19 +18092,19 @@
         <v>41</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18061,19 +18113,19 @@
         <v>42</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18082,19 +18134,19 @@
         <v>43</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18103,22 +18155,22 @@
         <v>44</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18127,19 +18179,19 @@
         <v>45</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18148,19 +18200,19 @@
         <v>46</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18169,22 +18221,22 @@
         <v>47</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E153" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="F153" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="F153" s="8" t="s">
-        <v>467</v>
-      </c>
       <c r="G153" s="8" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18193,19 +18245,19 @@
         <v>48</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18214,19 +18266,19 @@
         <v>49</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18235,22 +18287,22 @@
         <v>50</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18259,19 +18311,19 @@
         <v>51</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18280,19 +18332,19 @@
         <v>52</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18301,25 +18353,25 @@
         <v>53</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18328,19 +18380,19 @@
         <v>54</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18349,22 +18401,22 @@
         <v>55</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18373,19 +18425,19 @@
         <v>56</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18394,22 +18446,22 @@
         <v>57</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18418,22 +18470,22 @@
         <v>58</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18442,19 +18494,19 @@
         <v>59</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -18496,28 +18548,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="D1" s="37" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J1" s="37" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18526,10 +18578,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D2" s="55" t="n">
         <v>45849</v>
@@ -18565,10 +18617,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D3" s="55" t="n">
         <v>45849</v>
@@ -18604,10 +18656,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D4" s="55" t="n">
         <v>45849</v>
@@ -18643,10 +18695,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D5" s="57" t="n">
         <v>45849</v>
@@ -18682,10 +18734,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D6" s="57" t="n">
         <v>45849</v>
@@ -18721,10 +18773,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="D7" s="57" t="n">
         <v>45849</v>
@@ -18760,10 +18812,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D8" s="57" t="n">
         <v>45849</v>
@@ -18799,10 +18851,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D9" s="58" t="n">
         <v>45850</v>
@@ -18838,10 +18890,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D10" s="58" t="n">
         <v>45850</v>
@@ -18877,10 +18929,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D11" s="58" t="n">
         <v>45850</v>
@@ -18916,7 +18968,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="58" t="n">
@@ -18953,10 +19005,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D13" s="58"/>
       <c r="E13" s="17" t="n">
@@ -18990,10 +19042,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="60" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D14" s="58" t="n">
         <v>45850</v>
@@ -19029,10 +19081,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D15" s="58" t="n">
         <v>45850</v>
@@ -19068,10 +19120,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D16" s="58" t="n">
         <v>45850</v>
@@ -19107,10 +19159,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="17" t="n">
@@ -19144,10 +19196,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="17" t="n">
@@ -19181,10 +19233,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D19" s="58"/>
       <c r="E19" s="17" t="n">
@@ -19218,10 +19270,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D20" s="58"/>
       <c r="E20" s="17" t="n">
@@ -19255,10 +19307,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D21" s="58"/>
       <c r="E21" s="17" t="n">
@@ -19292,10 +19344,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D22" s="58"/>
       <c r="E22" s="17" t="n">
@@ -19329,10 +19381,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="17" t="n">
@@ -19366,10 +19418,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D24" s="58"/>
       <c r="E24" s="17" t="n">
@@ -19403,10 +19455,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D25" s="58"/>
       <c r="E25" s="17" t="n">
@@ -19440,10 +19492,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D26" s="58"/>
       <c r="E26" s="17" t="n">
@@ -19477,10 +19529,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D27" s="58"/>
       <c r="E27" s="17" t="n">
@@ -19514,10 +19566,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="D28" s="58"/>
       <c r="E28" s="17" t="n">
@@ -19551,10 +19603,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D29" s="58"/>
       <c r="E29" s="17" t="n">
@@ -19588,10 +19640,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="D30" s="58"/>
       <c r="E30" s="17" t="n">
@@ -19625,10 +19677,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="D31" s="58"/>
       <c r="E31" s="17" t="n">
@@ -19662,10 +19714,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D32" s="58"/>
       <c r="E32" s="17" t="n">
@@ -19699,10 +19751,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D33" s="58"/>
       <c r="E33" s="17" t="n">
@@ -19736,10 +19788,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="17" t="n">
@@ -19773,10 +19825,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="17" t="n">
@@ -19810,10 +19862,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D36" s="58"/>
       <c r="E36" s="17" t="n">
@@ -19847,10 +19899,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D37" s="58"/>
       <c r="E37" s="17" t="n">
@@ -19887,7 +19939,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D38" s="58"/>
       <c r="E38" s="17" t="n">
@@ -19921,10 +19973,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D39" s="58"/>
       <c r="E39" s="17" t="n">
@@ -19958,10 +20010,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D40" s="58"/>
       <c r="E40" s="17" t="n">
@@ -19995,10 +20047,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="D41" s="58"/>
       <c r="E41" s="17" t="n">
@@ -20032,7 +20084,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="58"/>
@@ -20067,7 +20119,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="58"/>
@@ -20102,7 +20154,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="58"/>
@@ -20137,10 +20189,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D45" s="58"/>
       <c r="E45" s="17" t="n">
@@ -20174,10 +20226,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D46" s="58"/>
       <c r="E46" s="17" t="n">
@@ -20211,10 +20263,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D47" s="58"/>
       <c r="E47" s="17" t="n">
@@ -20248,10 +20300,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D48" s="58"/>
       <c r="E48" s="17" t="n">
@@ -20285,10 +20337,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D49" s="58"/>
       <c r="E49" s="17" t="n">
@@ -20322,10 +20374,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D50" s="58"/>
       <c r="E50" s="17" t="n">
@@ -20359,10 +20411,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D51" s="58"/>
       <c r="E51" s="17" t="n">
@@ -20396,10 +20448,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D52" s="58"/>
       <c r="E52" s="17" t="n">
@@ -20433,10 +20485,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D53" s="58"/>
       <c r="E53" s="17" t="n">
@@ -20470,10 +20522,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="D54" s="58"/>
       <c r="E54" s="17" t="n">
@@ -20507,10 +20559,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="D55" s="58"/>
       <c r="E55" s="17" t="n">
@@ -20544,10 +20596,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D56" s="58"/>
       <c r="E56" s="17" t="n">
@@ -20581,10 +20633,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="D57" s="58"/>
       <c r="E57" s="17" t="n">
@@ -20618,10 +20670,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D58" s="58"/>
       <c r="E58" s="17" t="n">
@@ -20655,10 +20707,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="D59" s="58"/>
       <c r="E59" s="17" t="n">
@@ -20692,7 +20744,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C60" s="16"/>
       <c r="D60" s="58"/>
@@ -20727,10 +20779,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="D61" s="58"/>
       <c r="E61" s="17" t="n">
@@ -20764,10 +20816,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D62" s="58"/>
       <c r="E62" s="17" t="n">
@@ -20801,10 +20853,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D63" s="58"/>
       <c r="E63" s="17" t="n">
@@ -20838,10 +20890,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D64" s="58"/>
       <c r="E64" s="17" t="n">
@@ -20875,10 +20927,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="D65" s="58"/>
       <c r="E65" s="17" t="n">
@@ -20912,10 +20964,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D66" s="58"/>
       <c r="E66" s="17" t="n">
@@ -20949,10 +21001,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="61" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="D67" s="58"/>
       <c r="E67" s="17"/>
@@ -20968,10 +21020,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="61" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D68" s="58"/>
       <c r="E68" s="17"/>
@@ -20987,10 +21039,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="61" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="D69" s="58"/>
       <c r="E69" s="17"/>
@@ -21006,10 +21058,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="61" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D70" s="58"/>
       <c r="E70" s="17"/>
@@ -21025,10 +21077,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="61" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D71" s="58"/>
       <c r="E71" s="17"/>
@@ -25346,10 +25398,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="64" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B1" s="64" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C1" s="64"/>
       <c r="D1" s="64"/>
@@ -25361,10 +25413,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="66" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B2" s="67" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C2" s="67"/>
       <c r="D2" s="67"/>
@@ -25376,10 +25428,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="66" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C3" s="67"/>
       <c r="D3" s="67"/>
@@ -25391,10 +25443,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="66" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C4" s="67"/>
       <c r="D4" s="67"/>
@@ -25406,10 +25458,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="66" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B5" s="67" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C5" s="67"/>
       <c r="D5" s="67"/>
@@ -25421,10 +25473,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="66" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C6" s="67"/>
       <c r="D6" s="67"/>
@@ -25436,10 +25488,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="66" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="67"/>
@@ -25451,16 +25503,16 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="66" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="67"/>
       <c r="E8" s="67"/>
       <c r="F8" s="11" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="G8" s="65"/>
       <c r="H8" s="65"/>
@@ -25479,7 +25531,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C10" s="37" t="s">
         <v>4</v>
@@ -25500,7 +25552,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="68" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25509,7 +25561,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="69" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C11" s="17" t="n">
         <v>45855</v>
@@ -25545,7 +25597,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="70" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C12" s="17" t="n">
         <v>45855</v>

--- a/trackers/LCrev.xlsx
+++ b/trackers/LCrev.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="989">
   <si>
     <t xml:space="preserve">DSA-Notes</t>
   </si>
@@ -192,6 +192,15 @@
   </si>
   <si>
     <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">container-with-most-water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two pointers, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">left right pointer, and move the pointer on the shorter length(because inorder to increase area height must increase for next, because width is reducing anyway)</t>
   </si>
   <si>
     <t xml:space="preserve">Problem </t>
@@ -4645,12 +4654,24 @@
         <f aca="false">ROW()-2</f>
         <v>13</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="16"/>
+      <c r="B15" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>45887</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>24</v>
+      </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
@@ -8721,6 +8742,7 @@
     <hyperlink ref="B12" r:id="rId11" display="valid-palindrome"/>
     <hyperlink ref="B13" r:id="rId12" display="two-sum-ii-input-array-is-sorted"/>
     <hyperlink ref="B14" r:id="rId13" display="3Sum"/>
+    <hyperlink ref="B15" r:id="rId14" display="container-with-most-water"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -8746,167 +8768,167 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="77" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="77" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="77" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="77" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="77" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="77" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="77" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="77" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="77" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="77" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="77" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="77" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="77" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="77" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="77" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="77" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="77" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="77" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="77" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="77" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="77" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="77" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="77" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="77" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="77" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="77" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="77" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="77" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
     </row>
   </sheetData>
@@ -9002,94 +9024,94 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="78" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B1" s="79" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C1" s="79" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D2" s="80" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D3" s="80" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D4" s="80" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9098,40 +9120,40 @@
     </row>
     <row r="13" customFormat="false" ht="35.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="83" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="B13" s="83"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9140,211 +9162,211 @@
     </row>
     <row r="19" customFormat="false" ht="19.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="83" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B19" s="83"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="84" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B20" s="84"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="84" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B21" s="84"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="84" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B22" s="84"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="84" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B23" s="84"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="51" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="85" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="85" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B28" s="24" t="s">
+        <v>943</v>
+      </c>
+      <c r="C28" s="24" t="s">
         <v>940</v>
       </c>
-      <c r="C28" s="24" t="s">
-        <v>937</v>
-      </c>
       <c r="D28" s="24" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="51" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="85" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="85" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="85" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="85" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="85" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="85" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="85" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="85" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="85" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="85" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="24" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="24" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
     </row>
   </sheetData>
@@ -9389,7 +9411,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9398,10 +9420,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9410,10 +9432,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9422,10 +9444,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9434,10 +9456,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9446,10 +9468,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9458,10 +9480,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9470,10 +9492,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9482,10 +9504,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9494,7 +9516,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C10" s="48"/>
     </row>
@@ -9504,7 +9526,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C11" s="48"/>
     </row>
@@ -9514,7 +9536,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C12" s="48"/>
     </row>
@@ -9524,7 +9546,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C13" s="48"/>
     </row>
@@ -9763,12 +9785,12 @@
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="86" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
   </sheetData>
@@ -9800,10 +9822,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>3</v>
@@ -9815,10 +9837,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>14</v>
@@ -9833,7 +9855,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>14</v>
@@ -9848,7 +9870,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>14</v>
@@ -9863,7 +9885,7 @@
         <v>28</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>29</v>
@@ -9878,7 +9900,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>14</v>
@@ -12596,36 +12618,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B2" s="37" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12634,13 +12656,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12649,13 +12671,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12664,13 +12686,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12679,13 +12701,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12694,13 +12716,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12709,13 +12731,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12723,19 +12745,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B10" s="37" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12744,13 +12766,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12759,13 +12781,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12774,13 +12796,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12789,13 +12811,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12804,13 +12826,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12819,13 +12841,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12833,19 +12855,19 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B18" s="37" t="n">
         <v>15</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12854,13 +12876,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12869,13 +12891,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12884,13 +12906,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12899,13 +12921,13 @@
         <v>19</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12914,13 +12936,13 @@
         <v>20</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12929,13 +12951,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12943,19 +12965,19 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="36" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B26" s="37" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12964,13 +12986,13 @@
         <v>23</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12979,13 +13001,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12994,13 +13016,13 @@
         <v>25</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13009,13 +13031,13 @@
         <v>26</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13024,13 +13046,13 @@
         <v>27</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13039,13 +13061,13 @@
         <v>28</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13054,13 +13076,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13069,13 +13091,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13083,7 +13105,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -13096,13 +13118,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
@@ -13112,13 +13134,13 @@
         <v>3</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
@@ -13336,7 +13358,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -13349,13 +13371,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -13366,13 +13388,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -13383,13 +13405,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -13400,13 +13422,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -13417,13 +13439,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -13434,13 +13456,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -13451,13 +13473,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -13468,13 +13490,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -13485,13 +13507,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -13502,13 +13524,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -13519,13 +13541,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -13536,13 +13558,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -13553,13 +13575,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -13570,13 +13592,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -13587,13 +13609,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -13604,13 +13626,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -13621,13 +13643,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -13638,13 +13660,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -13655,13 +13677,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -13672,13 +13694,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -13689,13 +13711,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -13706,13 +13728,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -13772,22 +13794,22 @@
         <v>4</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H29" s="42" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13796,7 +13818,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>45729</v>
@@ -13832,7 +13854,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>45729</v>
@@ -13868,7 +13890,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="44" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>45729</v>
@@ -13904,7 +13926,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>45729</v>
@@ -13940,7 +13962,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C34" s="25" t="n">
         <v>45729</v>
@@ -13976,7 +13998,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C35" s="25" t="n">
         <v>45729</v>
@@ -14012,7 +14034,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C36" s="25" t="n">
         <v>45729</v>
@@ -14048,7 +14070,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C37" s="25" t="n">
         <v>45729</v>
@@ -14084,7 +14106,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C38" s="25" t="n">
         <v>45729</v>
@@ -14120,7 +14142,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C39" s="25" t="n">
         <v>45729</v>
@@ -14156,7 +14178,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C40" s="25" t="n">
         <v>45729</v>
@@ -14192,7 +14214,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C41" s="25" t="n">
         <v>45729</v>
@@ -14228,7 +14250,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C42" s="25" t="n">
         <v>45729</v>
@@ -14264,7 +14286,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C43" s="25" t="n">
         <v>45729</v>
@@ -14300,7 +14322,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="46" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C44" s="25" t="n">
         <v>45729</v>
@@ -14336,7 +14358,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="46" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C45" s="25" t="n">
         <v>45729</v>
@@ -14372,7 +14394,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="46" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C46" s="25" t="n">
         <v>45729</v>
@@ -14408,7 +14430,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="46" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C47" s="25" t="n">
         <v>45729</v>
@@ -14444,7 +14466,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="46" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C48" s="25" t="n">
         <v>45729</v>
@@ -14480,7 +14502,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="46" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C49" s="25" t="n">
         <v>45729</v>
@@ -14516,7 +14538,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C50" s="25" t="n">
         <v>45729</v>
@@ -14552,7 +14574,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C51" s="25" t="n">
         <v>45729</v>
@@ -14588,7 +14610,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="46" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C52" s="25" t="n">
         <v>45729</v>
@@ -14624,7 +14646,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="46" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C53" s="25" t="n">
         <v>45729</v>
@@ -14900,7 +14922,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q1" s="49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="R1" s="49"/>
       <c r="S1" s="49"/>
@@ -14908,119 +14930,119 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q2" s="35" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R2" s="35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="S2" s="35" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="T2" s="35" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q3" s="15" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q4" s="15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q6" s="15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="S6" s="15" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="T6" s="15" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q7" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="S7" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q8" s="15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q9" s="15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="S9" s="15" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q12" s="50" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="R12" s="50"/>
       <c r="S12" s="50"/>
@@ -15028,119 +15050,119 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q13" s="51" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R13" s="51" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="S13" s="51" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="T13" s="51" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q14" s="24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q15" s="24" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="T15" s="24" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q16" s="24" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="T16" s="24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q17" s="24" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="T17" s="24" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q18" s="24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="T18" s="24" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q19" s="24" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="R19" s="24" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="T19" s="24" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q20" s="24" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="R20" s="24" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="T20" s="24" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q23" s="50" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="R23" s="50"/>
       <c r="S23" s="50"/>
@@ -15148,119 +15170,119 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q24" s="51" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R24" s="51" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="S24" s="51" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="T24" s="51" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q25" s="24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="R25" s="24" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="S25" s="24" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="T25" s="24" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q26" s="24" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="S26" s="24" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="T26" s="24" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q27" s="24" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="R27" s="24" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="S27" s="24" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="T27" s="24" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q28" s="24" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="S28" s="24" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="T28" s="24" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q29" s="24" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="T29" s="24" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q30" s="24" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="R30" s="24" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="S30" s="24" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T30" s="24" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q31" s="24" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="R31" s="24" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="S31" s="24" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="T31" s="24" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q33" s="50" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="R33" s="50"/>
       <c r="S33" s="50"/>
@@ -15268,154 +15290,154 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q34" s="51" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R34" s="51" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="S34" s="51" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="T34" s="51" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q35" s="24" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="R35" s="24" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="S35" s="24" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="T35" s="24" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q36" s="24" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="R36" s="24" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="S36" s="24" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="T36" s="24" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q37" s="24" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="R37" s="24" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="S37" s="24" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="T37" s="24" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q38" s="24" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="R38" s="24" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="S38" s="24" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="T38" s="24" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q39" s="24" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="R39" s="24" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="S39" s="24" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="T39" s="24" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q40" s="24" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="R40" s="24" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="S40" s="24" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="T40" s="24" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q41" s="24" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="R41" s="24" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="S41" s="24" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="T41" s="24" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q44" s="52" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="R44" s="52"/>
       <c r="S44" s="52"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q45" s="51" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R45" s="51" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="S45" s="51" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q46" s="24" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="R46" s="24" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="S46" s="24" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q47" s="24" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="R47" s="24" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="S47" s="24" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -15452,291 +15474,291 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="53" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="54" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="54" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="54" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="54" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="54" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="54" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="53" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="54" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B13" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="C13" s="54" t="s">
         <v>396</v>
       </c>
-      <c r="C13" s="54" t="s">
-        <v>393</v>
-      </c>
       <c r="D13" s="54" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="54" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C15" s="54" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D15" s="54" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D16" s="54" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="54" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D17" s="54" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="55" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="35" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C23" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C24" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C26" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -15770,13 +15792,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -15788,13 +15810,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E2" s="57" t="s">
         <v>14</v>
@@ -15806,13 +15828,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E3" s="57" t="s">
         <v>14</v>
@@ -15824,13 +15846,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>29</v>
@@ -15842,13 +15864,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E5" s="57" t="s">
         <v>14</v>
@@ -15860,13 +15882,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>29</v>
@@ -15878,13 +15900,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>29</v>
@@ -15896,13 +15918,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>29</v>
@@ -15914,13 +15936,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E9" s="57" t="s">
         <v>29</v>
@@ -15932,13 +15954,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E10" s="57" t="s">
         <v>14</v>
@@ -15950,13 +15972,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E11" s="57" t="s">
         <v>29</v>
@@ -15968,13 +15990,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E12" s="57" t="s">
         <v>29</v>
@@ -15986,13 +16008,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C13" s="56" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E13" s="57" t="s">
         <v>29</v>
@@ -16004,13 +16026,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E14" s="57" t="s">
         <v>14</v>
@@ -16022,13 +16044,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E15" s="57" t="s">
         <v>14</v>
@@ -16040,13 +16062,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E16" s="57" t="s">
         <v>14</v>
@@ -16058,13 +16080,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E17" s="57" t="s">
         <v>14</v>
@@ -16076,13 +16098,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>14</v>
@@ -16094,13 +16116,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E19" s="57" t="s">
         <v>29</v>
@@ -16112,13 +16134,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E20" s="57" t="s">
         <v>14</v>
@@ -16130,13 +16152,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C21" s="56" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E21" s="57" t="s">
         <v>29</v>
@@ -16148,13 +16170,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E22" s="57" t="s">
         <v>29</v>
@@ -16166,13 +16188,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E23" s="57" t="s">
         <v>29</v>
@@ -16184,13 +16206,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C24" s="56" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E24" s="57" t="s">
         <v>14</v>
@@ -16202,13 +16224,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E25" s="57" t="s">
         <v>14</v>
@@ -16220,13 +16242,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E26" s="57" t="s">
         <v>29</v>
@@ -16238,13 +16260,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C27" s="56" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E27" s="57" t="s">
         <v>14</v>
@@ -16256,16 +16278,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E28" s="57" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16274,16 +16296,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D29" s="56" t="s">
+        <v>493</v>
+      </c>
+      <c r="E29" s="57" t="s">
         <v>490</v>
-      </c>
-      <c r="E29" s="57" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16292,13 +16314,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E30" s="57" t="s">
         <v>29</v>
@@ -16310,13 +16332,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E31" s="57" t="s">
         <v>29</v>
@@ -16328,13 +16350,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E32" s="57" t="s">
         <v>29</v>
@@ -16346,13 +16368,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E33" s="57" t="s">
         <v>29</v>
@@ -16364,13 +16386,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C34" s="56" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E34" s="57" t="s">
         <v>29</v>
@@ -16382,13 +16404,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E35" s="57" t="s">
         <v>14</v>
@@ -16400,13 +16422,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C36" s="56" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E36" s="57" t="s">
         <v>29</v>
@@ -16418,13 +16440,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C37" s="56" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E37" s="57" t="s">
         <v>29</v>
@@ -16436,13 +16458,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C38" s="56" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E38" s="57" t="s">
         <v>29</v>
@@ -16454,13 +16476,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C39" s="56" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D39" s="56" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E39" s="57" t="s">
         <v>29</v>
@@ -16472,13 +16494,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C40" s="56" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D40" s="56" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E40" s="57" t="s">
         <v>29</v>
@@ -16490,13 +16512,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C41" s="56" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D41" s="56" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E41" s="57" t="s">
         <v>29</v>
@@ -16508,13 +16530,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="56" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C42" s="56" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D42" s="56" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E42" s="57" t="s">
         <v>29</v>
@@ -16526,16 +16548,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="56" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C43" s="56" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D43" s="56" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E43" s="57" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16544,13 +16566,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="56" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C44" s="56" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D44" s="56" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E44" s="57" t="s">
         <v>14</v>
@@ -16562,13 +16584,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="56" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C45" s="56" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D45" s="56" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E45" s="57" t="s">
         <v>14</v>
@@ -16580,13 +16602,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="56" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C46" s="56" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D46" s="56" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E46" s="57" t="s">
         <v>14</v>
@@ -16598,13 +16620,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="56" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C47" s="56" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D47" s="56" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E47" s="57" t="s">
         <v>29</v>
@@ -16616,13 +16638,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="56" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C48" s="56" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D48" s="56" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E48" s="57" t="s">
         <v>29</v>
@@ -16634,13 +16656,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="56" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C49" s="56" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D49" s="56" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E49" s="57" t="s">
         <v>29</v>
@@ -16649,13 +16671,13 @@
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>3</v>
@@ -16667,13 +16689,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>14</v>
@@ -16685,13 +16707,13 @@
         <v>2</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>14</v>
@@ -16703,13 +16725,13 @@
         <v>3</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>29</v>
@@ -16721,13 +16743,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>14</v>
@@ -16739,13 +16761,13 @@
         <v>5</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>29</v>
@@ -16757,13 +16779,13 @@
         <v>6</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>29</v>
@@ -16775,13 +16797,13 @@
         <v>7</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>29</v>
@@ -16793,13 +16815,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>14</v>
@@ -16811,13 +16833,13 @@
         <v>9</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>29</v>
@@ -16829,13 +16851,13 @@
         <v>10</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>29</v>
@@ -16847,13 +16869,13 @@
         <v>11</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>14</v>
@@ -16865,13 +16887,13 @@
         <v>12</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>14</v>
@@ -16883,13 +16905,13 @@
         <v>13</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>14</v>
@@ -16901,13 +16923,13 @@
         <v>14</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>14</v>
@@ -16919,13 +16941,13 @@
         <v>15</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>29</v>
@@ -16937,13 +16959,13 @@
         <v>16</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>14</v>
@@ -16955,13 +16977,13 @@
         <v>17</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>29</v>
@@ -16973,13 +16995,13 @@
         <v>18</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>29</v>
@@ -16991,13 +17013,13 @@
         <v>19</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>29</v>
@@ -17009,13 +17031,13 @@
         <v>20</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>14</v>
@@ -17027,13 +17049,13 @@
         <v>21</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>14</v>
@@ -17045,13 +17067,13 @@
         <v>22</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>14</v>
@@ -17063,13 +17085,13 @@
         <v>23</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>29</v>
@@ -17081,13 +17103,13 @@
         <v>24</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>14</v>
@@ -17099,16 +17121,16 @@
         <v>25</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17117,16 +17139,16 @@
         <v>26</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D77" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="E77" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17135,13 +17157,13 @@
         <v>27</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>29</v>
@@ -17153,13 +17175,13 @@
         <v>28</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>29</v>
@@ -17171,13 +17193,13 @@
         <v>29</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>29</v>
@@ -17189,13 +17211,13 @@
         <v>30</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>29</v>
@@ -17207,13 +17229,13 @@
         <v>31</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>29</v>
@@ -17225,13 +17247,13 @@
         <v>32</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>29</v>
@@ -17243,16 +17265,16 @@
         <v>33</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17261,13 +17283,13 @@
         <v>34</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>29</v>
@@ -17279,13 +17301,13 @@
         <v>35</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>14</v>
@@ -17297,13 +17319,13 @@
         <v>36</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>29</v>
@@ -17315,13 +17337,13 @@
         <v>37</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>29</v>
@@ -17333,13 +17355,13 @@
         <v>38</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>29</v>
@@ -17351,13 +17373,13 @@
         <v>39</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>29</v>
@@ -17369,13 +17391,13 @@
         <v>40</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>29</v>
@@ -17387,13 +17409,13 @@
         <v>41</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>29</v>
@@ -17405,13 +17427,13 @@
         <v>42</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>29</v>
@@ -17423,13 +17445,13 @@
         <v>43</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>29</v>
@@ -17441,13 +17463,13 @@
         <v>44</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>29</v>
@@ -17459,16 +17481,16 @@
         <v>45</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>29</v>
@@ -17480,16 +17502,16 @@
         <v>46</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>29</v>
@@ -17501,16 +17523,16 @@
         <v>47</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>29</v>
@@ -17522,19 +17544,19 @@
         <v>48</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17543,16 +17565,16 @@
         <v>49</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>14</v>
@@ -17564,16 +17586,16 @@
         <v>50</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>14</v>
@@ -17584,22 +17606,22 @@
         <v>1</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="H106" s="9"/>
     </row>
@@ -17609,22 +17631,22 @@
         <v>1</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17633,19 +17655,19 @@
         <v>2</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17654,19 +17676,19 @@
         <v>3</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17675,19 +17697,19 @@
         <v>4</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17696,22 +17718,22 @@
         <v>5</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17720,22 +17742,22 @@
         <v>6</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17744,19 +17766,19 @@
         <v>7</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17765,22 +17787,22 @@
         <v>8</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17789,19 +17811,19 @@
         <v>9</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17810,19 +17832,19 @@
         <v>10</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17831,22 +17853,22 @@
         <v>11</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17855,19 +17877,19 @@
         <v>12</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17876,19 +17898,19 @@
         <v>13</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17897,22 +17919,22 @@
         <v>14</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17921,19 +17943,19 @@
         <v>15</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17942,19 +17964,19 @@
         <v>16</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17963,22 +17985,22 @@
         <v>17</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>48</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17987,19 +18009,19 @@
         <v>18</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18008,19 +18030,19 @@
         <v>19</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18029,28 +18051,28 @@
         <v>20</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18059,19 +18081,19 @@
         <v>21</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18080,19 +18102,19 @@
         <v>22</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18101,25 +18123,25 @@
         <v>23</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>14</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18128,19 +18150,19 @@
         <v>24</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18149,19 +18171,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18170,22 +18192,22 @@
         <v>26</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18194,19 +18216,19 @@
         <v>27</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18215,19 +18237,19 @@
         <v>28</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18236,22 +18258,22 @@
         <v>29</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18260,19 +18282,19 @@
         <v>30</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18281,19 +18303,19 @@
         <v>31</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18302,19 +18324,19 @@
         <v>32</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18323,28 +18345,28 @@
         <v>33</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>29</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18353,19 +18375,19 @@
         <v>34</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18374,19 +18396,19 @@
         <v>35</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18395,25 +18417,25 @@
         <v>36</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18422,19 +18444,19 @@
         <v>37</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18443,19 +18465,19 @@
         <v>38</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18464,31 +18486,31 @@
         <v>39</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18497,19 +18519,19 @@
         <v>40</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18518,19 +18540,19 @@
         <v>41</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18539,19 +18561,19 @@
         <v>42</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18560,19 +18582,19 @@
         <v>43</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18581,22 +18603,22 @@
         <v>44</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18605,19 +18627,19 @@
         <v>45</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18626,19 +18648,19 @@
         <v>46</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18647,22 +18669,22 @@
         <v>47</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E153" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="F153" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="F153" s="8" t="s">
-        <v>487</v>
-      </c>
       <c r="G153" s="8" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18671,19 +18693,19 @@
         <v>48</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18692,19 +18714,19 @@
         <v>49</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18713,22 +18735,22 @@
         <v>50</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18737,19 +18759,19 @@
         <v>51</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18758,19 +18780,19 @@
         <v>52</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18779,25 +18801,25 @@
         <v>53</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18806,19 +18828,19 @@
         <v>54</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18827,22 +18849,22 @@
         <v>55</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18851,19 +18873,19 @@
         <v>56</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18872,22 +18894,22 @@
         <v>57</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18896,22 +18918,22 @@
         <v>58</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18920,19 +18942,19 @@
         <v>59</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -18974,28 +18996,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D1" s="42" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19004,10 +19026,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D2" s="59" t="n">
         <v>45849</v>
@@ -19043,10 +19065,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D3" s="59" t="n">
         <v>45849</v>
@@ -19082,10 +19104,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D4" s="59" t="n">
         <v>45849</v>
@@ -19121,10 +19143,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D5" s="61" t="n">
         <v>45849</v>
@@ -19160,10 +19182,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D6" s="61" t="n">
         <v>45849</v>
@@ -19199,10 +19221,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D7" s="61" t="n">
         <v>45849</v>
@@ -19238,10 +19260,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D8" s="61" t="n">
         <v>45849</v>
@@ -19277,10 +19299,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D9" s="62" t="n">
         <v>45850</v>
@@ -19316,10 +19338,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D10" s="62" t="n">
         <v>45850</v>
@@ -19355,10 +19377,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D11" s="62" t="n">
         <v>45850</v>
@@ -19394,7 +19416,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="62" t="n">
@@ -19431,10 +19453,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D13" s="62"/>
       <c r="E13" s="17" t="n">
@@ -19468,10 +19490,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="D14" s="62" t="n">
         <v>45850</v>
@@ -19507,10 +19529,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D15" s="62" t="n">
         <v>45850</v>
@@ -19546,10 +19568,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="D16" s="62" t="n">
         <v>45850</v>
@@ -19585,10 +19607,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D17" s="62"/>
       <c r="E17" s="17" t="n">
@@ -19622,10 +19644,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D18" s="62"/>
       <c r="E18" s="17" t="n">
@@ -19659,10 +19681,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D19" s="62"/>
       <c r="E19" s="17" t="n">
@@ -19696,10 +19718,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="D20" s="62"/>
       <c r="E20" s="17" t="n">
@@ -19733,10 +19755,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D21" s="62"/>
       <c r="E21" s="17" t="n">
@@ -19770,10 +19792,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="D22" s="62"/>
       <c r="E22" s="17" t="n">
@@ -19807,10 +19829,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="D23" s="62"/>
       <c r="E23" s="17" t="n">
@@ -19844,10 +19866,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D24" s="62"/>
       <c r="E24" s="17" t="n">
@@ -19881,10 +19903,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="D25" s="62"/>
       <c r="E25" s="17" t="n">
@@ -19918,10 +19940,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D26" s="62"/>
       <c r="E26" s="17" t="n">
@@ -19955,10 +19977,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D27" s="62"/>
       <c r="E27" s="17" t="n">
@@ -19992,10 +20014,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="D28" s="62"/>
       <c r="E28" s="17" t="n">
@@ -20029,10 +20051,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D29" s="62"/>
       <c r="E29" s="17" t="n">
@@ -20066,10 +20088,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D30" s="62"/>
       <c r="E30" s="17" t="n">
@@ -20103,10 +20125,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="D31" s="62"/>
       <c r="E31" s="17" t="n">
@@ -20140,10 +20162,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D32" s="62"/>
       <c r="E32" s="17" t="n">
@@ -20177,10 +20199,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D33" s="62"/>
       <c r="E33" s="17" t="n">
@@ -20214,10 +20236,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D34" s="62"/>
       <c r="E34" s="17" t="n">
@@ -20251,10 +20273,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D35" s="62"/>
       <c r="E35" s="17" t="n">
@@ -20288,10 +20310,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D36" s="62"/>
       <c r="E36" s="17" t="n">
@@ -20325,10 +20347,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="D37" s="62"/>
       <c r="E37" s="17" t="n">
@@ -20365,7 +20387,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D38" s="62"/>
       <c r="E38" s="17" t="n">
@@ -20399,10 +20421,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D39" s="62"/>
       <c r="E39" s="17" t="n">
@@ -20436,10 +20458,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D40" s="62"/>
       <c r="E40" s="17" t="n">
@@ -20473,10 +20495,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D41" s="62"/>
       <c r="E41" s="17" t="n">
@@ -20510,7 +20532,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="62"/>
@@ -20545,7 +20567,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="62"/>
@@ -20580,7 +20602,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="62"/>
@@ -20615,10 +20637,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="17" t="n">
@@ -20652,10 +20674,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="D46" s="62"/>
       <c r="E46" s="17" t="n">
@@ -20689,10 +20711,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D47" s="62"/>
       <c r="E47" s="17" t="n">
@@ -20726,10 +20748,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D48" s="62"/>
       <c r="E48" s="17" t="n">
@@ -20763,10 +20785,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="D49" s="62"/>
       <c r="E49" s="17" t="n">
@@ -20800,10 +20822,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D50" s="62"/>
       <c r="E50" s="17" t="n">
@@ -20837,10 +20859,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="D51" s="62"/>
       <c r="E51" s="17" t="n">
@@ -20874,10 +20896,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D52" s="62"/>
       <c r="E52" s="17" t="n">
@@ -20911,10 +20933,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D53" s="62"/>
       <c r="E53" s="17" t="n">
@@ -20948,10 +20970,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D54" s="62"/>
       <c r="E54" s="17" t="n">
@@ -20985,10 +21007,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="D55" s="62"/>
       <c r="E55" s="17" t="n">
@@ -21022,10 +21044,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D56" s="62"/>
       <c r="E56" s="17" t="n">
@@ -21059,10 +21081,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="D57" s="62"/>
       <c r="E57" s="17" t="n">
@@ -21096,10 +21118,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D58" s="62"/>
       <c r="E58" s="17" t="n">
@@ -21133,10 +21155,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="D59" s="62"/>
       <c r="E59" s="17" t="n">
@@ -21170,7 +21192,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C60" s="16"/>
       <c r="D60" s="62"/>
@@ -21205,10 +21227,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="D61" s="62"/>
       <c r="E61" s="17" t="n">
@@ -21242,10 +21264,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D62" s="62"/>
       <c r="E62" s="17" t="n">
@@ -21279,10 +21301,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D63" s="62"/>
       <c r="E63" s="17" t="n">
@@ -21316,10 +21338,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D64" s="62"/>
       <c r="E64" s="17" t="n">
@@ -21353,10 +21375,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D65" s="62"/>
       <c r="E65" s="17" t="n">
@@ -21390,10 +21412,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D66" s="62"/>
       <c r="E66" s="17" t="n">
@@ -21427,10 +21449,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="65" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D67" s="62"/>
       <c r="E67" s="17"/>
@@ -21446,10 +21468,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="65" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D68" s="62"/>
       <c r="E68" s="17"/>
@@ -21465,10 +21487,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="65" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D69" s="62"/>
       <c r="E69" s="17"/>
@@ -21484,10 +21506,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="D70" s="62"/>
       <c r="E70" s="17"/>
@@ -21503,10 +21525,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="65" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D71" s="62"/>
       <c r="E71" s="17"/>
@@ -25824,10 +25846,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="68" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
@@ -25839,10 +25861,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="70" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C2" s="71"/>
       <c r="D2" s="71"/>
@@ -25854,10 +25876,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="70" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C3" s="71"/>
       <c r="D3" s="71"/>
@@ -25869,10 +25891,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="70" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
@@ -25884,10 +25906,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="70" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
@@ -25899,10 +25921,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="70" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
@@ -25914,10 +25936,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="70" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
@@ -25929,16 +25951,16 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="70" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C8" s="71"/>
       <c r="D8" s="71"/>
       <c r="E8" s="71"/>
       <c r="F8" s="11" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="G8" s="69"/>
       <c r="H8" s="69"/>
@@ -25957,7 +25979,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C10" s="42" t="s">
         <v>4</v>
@@ -25978,7 +26000,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="72" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25987,7 +26009,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="73" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C11" s="17" t="n">
         <v>45855</v>
@@ -26023,7 +26045,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="74" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C12" s="17" t="n">
         <v>45855</v>
@@ -26060,7 +26082,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="74" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C13" s="75"/>
       <c r="D13" s="17"/>

--- a/trackers/LCrev.xlsx
+++ b/trackers/LCrev.xlsx
@@ -4672,11 +4672,26 @@
       <c r="G15" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="31"/>
+      <c r="H15" s="13" t="n">
+        <f aca="false">D15+2</f>
+        <v>45889</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <f aca="false">D15+7</f>
+        <v>45894</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <f aca="false">D15+21</f>
+        <v>45908</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <f aca="false">D15+45</f>
+        <v>45932</v>
+      </c>
+      <c r="L15" s="18" t="n">
+        <f aca="false">D15+60</f>
+        <v>45947</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="n">

--- a/trackers/LCrev.xlsx
+++ b/trackers/LCrev.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="998">
   <si>
     <t xml:space="preserve">DSA-Notes</t>
   </si>
@@ -201,6 +201,33 @@
   </si>
   <si>
     <t xml:space="preserve">left right pointer, and move the pointer on the shorter length(because inorder to increase area height must increase for next, because width is reducing anyway)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minimum-add-to-make-parentheses-valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">track no.of left,right parenthesis &amp; return sum in the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">implement-queue-using-stacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 stacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">every push, s1-&gt;st2, s1.push(x), st2-&gt;st1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">next-greater-element-i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monotonically decreasing stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mds &amp; map, if new large element found pop, if not found then it will be in stacl</t>
   </si>
   <si>
     <t xml:space="preserve">Problem </t>
@@ -4698,51 +4725,132 @@
         <f aca="false">ROW()-2</f>
         <v>14</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="31"/>
+      <c r="B16" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>45888</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <f aca="false">D16+2</f>
+        <v>45890</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <f aca="false">D16+7</f>
+        <v>45895</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <f aca="false">D16+21</f>
+        <v>45909</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <f aca="false">D16+45</f>
+        <v>45933</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <f aca="false">D16+60</f>
+        <v>45948</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="n">
         <f aca="false">ROW()-2</f>
         <v>15</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="31"/>
+      <c r="B17" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>45888</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <f aca="false">D17+2</f>
+        <v>45890</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <f aca="false">D17+7</f>
+        <v>45895</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <f aca="false">D17+21</f>
+        <v>45909</v>
+      </c>
+      <c r="K17" s="17" t="n">
+        <f aca="false">D17+45</f>
+        <v>45933</v>
+      </c>
+      <c r="L17" s="18" t="n">
+        <f aca="false">D17+60</f>
+        <v>45948</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="n">
         <f aca="false">ROW()-2</f>
         <v>16</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="31"/>
+      <c r="B18" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>45888</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <f aca="false">D18+2</f>
+        <v>45890</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <f aca="false">D18+7</f>
+        <v>45895</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <f aca="false">D18+21</f>
+        <v>45909</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <f aca="false">D18+45</f>
+        <v>45933</v>
+      </c>
+      <c r="L18" s="18" t="n">
+        <f aca="false">D18+60</f>
+        <v>45948</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="n">
@@ -8758,6 +8866,9 @@
     <hyperlink ref="B13" r:id="rId12" display="two-sum-ii-input-array-is-sorted"/>
     <hyperlink ref="B14" r:id="rId13" display="3Sum"/>
     <hyperlink ref="B15" r:id="rId14" display="container-with-most-water"/>
+    <hyperlink ref="B16" r:id="rId15" display="minimum-add-to-make-parentheses-valid"/>
+    <hyperlink ref="B17" r:id="rId16" display="implement-queue-using-stacks"/>
+    <hyperlink ref="B18" r:id="rId17" display="next-greater-element-i"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -8783,167 +8894,167 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="77" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="77" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="77" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="77" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="77" t="s">
-        <v>868</v>
+        <v>877</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="77" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="77" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="77" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="77" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="77" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="77" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="77" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="77" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="77" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="77" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="77" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="77" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="77" t="s">
-        <v>883</v>
+        <v>892</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="77" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="77" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="77" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="77" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="77" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="77" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="77" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="77" t="s">
-        <v>892</v>
+        <v>901</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="77" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="77" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
     </row>
   </sheetData>
@@ -9039,94 +9150,94 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="78" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
       <c r="B1" s="79" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="C1" s="79" t="s">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="D2" s="80" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="D3" s="80" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="D4" s="80" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>917</v>
+        <v>926</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>918</v>
+        <v>927</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>919</v>
+        <v>928</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>920</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9135,40 +9246,40 @@
     </row>
     <row r="13" customFormat="false" ht="35.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="83" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
       <c r="B13" s="83"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>922</v>
+        <v>931</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>924</v>
+        <v>933</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>925</v>
+        <v>934</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>926</v>
+        <v>935</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>927</v>
+        <v>936</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>928</v>
+        <v>937</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>929</v>
+        <v>938</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9177,211 +9288,211 @@
     </row>
     <row r="19" customFormat="false" ht="19.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="83" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="B19" s="83"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="84" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="B20" s="84"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="84" t="s">
-        <v>932</v>
+        <v>941</v>
       </c>
       <c r="B21" s="84"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="84" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="B22" s="84"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="84" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="B23" s="84"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="51" t="s">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>936</v>
+        <v>945</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>937</v>
+        <v>946</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>938</v>
+        <v>947</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="85" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>940</v>
+        <v>949</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>941</v>
+        <v>950</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="85" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>943</v>
+        <v>952</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>940</v>
+        <v>949</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="51" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>947</v>
+        <v>956</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="85" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>950</v>
+        <v>959</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="85" t="s">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>953</v>
+        <v>962</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="85" t="s">
-        <v>954</v>
+        <v>963</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="85" t="s">
-        <v>957</v>
+        <v>966</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>959</v>
+        <v>968</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="85" t="s">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>962</v>
+        <v>971</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="85" t="s">
-        <v>963</v>
+        <v>972</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>964</v>
+        <v>973</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>965</v>
+        <v>974</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="85" t="s">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>967</v>
+        <v>976</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="85" t="s">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>970</v>
+        <v>979</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>971</v>
+        <v>980</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="85" t="s">
-        <v>972</v>
+        <v>981</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="85" t="s">
-        <v>975</v>
+        <v>984</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>977</v>
+        <v>986</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="24" t="s">
-        <v>978</v>
+        <v>987</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="24" t="s">
-        <v>979</v>
+        <v>988</v>
       </c>
     </row>
   </sheetData>
@@ -9426,7 +9537,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9435,10 +9546,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>980</v>
+        <v>989</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9447,10 +9558,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9459,10 +9570,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>981</v>
+        <v>990</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9471,10 +9582,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9483,10 +9594,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9495,10 +9606,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9507,10 +9618,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>983</v>
+        <v>992</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9519,10 +9630,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>984</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9531,7 +9642,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>985</v>
+        <v>994</v>
       </c>
       <c r="C10" s="48"/>
     </row>
@@ -9541,7 +9652,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>986</v>
+        <v>995</v>
       </c>
       <c r="C11" s="48"/>
     </row>
@@ -9551,7 +9662,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="C12" s="48"/>
     </row>
@@ -9561,7 +9672,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="C13" s="48"/>
     </row>
@@ -9800,12 +9911,12 @@
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="86" t="s">
-        <v>987</v>
+        <v>996</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>988</v>
+        <v>997</v>
       </c>
     </row>
   </sheetData>
@@ -9837,10 +9948,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>3</v>
@@ -9852,10 +9963,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>14</v>
@@ -9870,7 +9981,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>14</v>
@@ -9885,7 +9996,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>14</v>
@@ -9900,7 +10011,7 @@
         <v>28</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>29</v>
@@ -9915,7 +10026,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>14</v>
@@ -12633,36 +12744,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B2" s="37" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12671,13 +12782,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12686,13 +12797,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12701,13 +12812,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12716,13 +12827,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12731,13 +12842,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12746,13 +12857,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12760,19 +12871,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B10" s="37" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12781,13 +12892,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12796,13 +12907,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12811,13 +12922,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12826,13 +12937,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12841,13 +12952,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12856,13 +12967,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12870,19 +12981,19 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B18" s="37" t="n">
         <v>15</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12891,13 +13002,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12906,13 +13017,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12921,13 +13032,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12936,13 +13047,13 @@
         <v>19</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12951,13 +13062,13 @@
         <v>20</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12966,13 +13077,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12980,19 +13091,19 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="36" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B26" s="37" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13001,13 +13112,13 @@
         <v>23</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13016,13 +13127,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13031,13 +13142,13 @@
         <v>25</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13046,13 +13157,13 @@
         <v>26</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13061,13 +13172,13 @@
         <v>27</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13076,13 +13187,13 @@
         <v>28</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13091,13 +13202,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13106,13 +13217,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13120,7 +13231,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -13133,13 +13244,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
@@ -13149,13 +13260,13 @@
         <v>3</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
@@ -13373,7 +13484,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -13386,13 +13497,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -13403,13 +13514,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -13420,13 +13531,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -13437,13 +13548,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -13454,13 +13565,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -13471,13 +13582,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -13488,13 +13599,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -13505,13 +13616,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -13522,13 +13633,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -13539,13 +13650,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -13556,13 +13667,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -13573,13 +13684,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -13590,13 +13701,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -13607,13 +13718,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -13624,13 +13735,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -13641,13 +13752,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -13658,13 +13769,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -13675,13 +13786,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -13692,13 +13803,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -13709,13 +13820,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -13726,13 +13837,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -13743,13 +13854,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -13809,22 +13920,22 @@
         <v>4</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H29" s="42" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13833,7 +13944,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>45729</v>
@@ -13869,7 +13980,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>45729</v>
@@ -13905,7 +14016,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="44" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>45729</v>
@@ -13941,7 +14052,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>45729</v>
@@ -13977,7 +14088,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C34" s="25" t="n">
         <v>45729</v>
@@ -14013,7 +14124,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C35" s="25" t="n">
         <v>45729</v>
@@ -14049,7 +14160,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C36" s="25" t="n">
         <v>45729</v>
@@ -14085,7 +14196,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C37" s="25" t="n">
         <v>45729</v>
@@ -14121,7 +14232,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C38" s="25" t="n">
         <v>45729</v>
@@ -14157,7 +14268,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C39" s="25" t="n">
         <v>45729</v>
@@ -14193,7 +14304,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C40" s="25" t="n">
         <v>45729</v>
@@ -14229,7 +14340,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="C41" s="25" t="n">
         <v>45729</v>
@@ -14265,7 +14376,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C42" s="25" t="n">
         <v>45729</v>
@@ -14301,7 +14412,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C43" s="25" t="n">
         <v>45729</v>
@@ -14337,7 +14448,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="46" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C44" s="25" t="n">
         <v>45729</v>
@@ -14373,7 +14484,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="46" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C45" s="25" t="n">
         <v>45729</v>
@@ -14409,7 +14520,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="46" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="C46" s="25" t="n">
         <v>45729</v>
@@ -14445,7 +14556,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="46" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="C47" s="25" t="n">
         <v>45729</v>
@@ -14481,7 +14592,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="46" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C48" s="25" t="n">
         <v>45729</v>
@@ -14517,7 +14628,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="46" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C49" s="25" t="n">
         <v>45729</v>
@@ -14553,7 +14664,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C50" s="25" t="n">
         <v>45729</v>
@@ -14589,7 +14700,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C51" s="25" t="n">
         <v>45729</v>
@@ -14625,7 +14736,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="46" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C52" s="25" t="n">
         <v>45729</v>
@@ -14661,7 +14772,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="46" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C53" s="25" t="n">
         <v>45729</v>
@@ -14937,7 +15048,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q1" s="49" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="R1" s="49"/>
       <c r="S1" s="49"/>
@@ -14945,119 +15056,119 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q2" s="35" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="R2" s="35" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="S2" s="35" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="T2" s="35" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q3" s="15" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q4" s="15" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="15" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q6" s="15" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="S6" s="15" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="T6" s="15" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q7" s="15" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="S7" s="15" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q8" s="15" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q9" s="15" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="S9" s="15" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q12" s="50" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="R12" s="50"/>
       <c r="S12" s="50"/>
@@ -15065,119 +15176,119 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q13" s="51" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="R13" s="51" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="S13" s="51" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="T13" s="51" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q14" s="24" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q15" s="24" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="T15" s="24" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q16" s="24" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="T16" s="24" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q17" s="24" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="T17" s="24" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q18" s="24" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="T18" s="24" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q19" s="24" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="R19" s="24" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="T19" s="24" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q20" s="24" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="R20" s="24" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="T20" s="24" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q23" s="50" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="R23" s="50"/>
       <c r="S23" s="50"/>
@@ -15185,119 +15296,119 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q24" s="51" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="R24" s="51" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="S24" s="51" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="T24" s="51" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q25" s="24" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="R25" s="24" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="S25" s="24" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="T25" s="24" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q26" s="24" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="S26" s="24" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="T26" s="24" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q27" s="24" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="R27" s="24" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="S27" s="24" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="T27" s="24" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q28" s="24" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="S28" s="24" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="T28" s="24" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q29" s="24" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="T29" s="24" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q30" s="24" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="R30" s="24" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="S30" s="24" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="T30" s="24" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q31" s="24" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="R31" s="24" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="S31" s="24" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="T31" s="24" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q33" s="50" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="R33" s="50"/>
       <c r="S33" s="50"/>
@@ -15305,154 +15416,154 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q34" s="51" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="R34" s="51" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="S34" s="51" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="T34" s="51" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q35" s="24" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="R35" s="24" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="S35" s="24" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="T35" s="24" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q36" s="24" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="R36" s="24" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="S36" s="24" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="T36" s="24" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q37" s="24" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="R37" s="24" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="S37" s="24" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="T37" s="24" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q38" s="24" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="R38" s="24" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="S38" s="24" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="T38" s="24" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q39" s="24" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="R39" s="24" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="S39" s="24" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="T39" s="24" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q40" s="24" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="R40" s="24" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="S40" s="24" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="T40" s="24" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q41" s="24" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="R41" s="24" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="S41" s="24" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="T41" s="24" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q44" s="52" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="R44" s="52"/>
       <c r="S44" s="52"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q45" s="51" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="R45" s="51" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="S45" s="51" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q46" s="24" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="R46" s="24" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="S46" s="24" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q47" s="24" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="R47" s="24" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="S47" s="24" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -15489,291 +15600,291 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="53" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="54" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="54" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="54" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="54" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="54" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="54" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="53" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="54" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D13" s="54" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="54" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C15" s="54" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D15" s="54" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="D16" s="54" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="54" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="D17" s="54" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="55" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="35" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C23" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C24" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C26" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -15807,13 +15918,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -15825,13 +15936,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E2" s="57" t="s">
         <v>14</v>
@@ -15843,13 +15954,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="E3" s="57" t="s">
         <v>14</v>
@@ -15861,13 +15972,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>29</v>
@@ -15879,13 +15990,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="E5" s="57" t="s">
         <v>14</v>
@@ -15897,13 +16008,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>29</v>
@@ -15915,13 +16026,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>29</v>
@@ -15933,13 +16044,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>29</v>
@@ -15951,13 +16062,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="E9" s="57" t="s">
         <v>29</v>
@@ -15969,13 +16080,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E10" s="57" t="s">
         <v>14</v>
@@ -15987,13 +16098,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="E11" s="57" t="s">
         <v>29</v>
@@ -16005,13 +16116,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="E12" s="57" t="s">
         <v>29</v>
@@ -16023,13 +16134,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C13" s="56" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E13" s="57" t="s">
         <v>29</v>
@@ -16041,13 +16152,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="E14" s="57" t="s">
         <v>14</v>
@@ -16059,13 +16170,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="E15" s="57" t="s">
         <v>14</v>
@@ -16077,13 +16188,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="E16" s="57" t="s">
         <v>14</v>
@@ -16095,13 +16206,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="E17" s="57" t="s">
         <v>14</v>
@@ -16113,13 +16224,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>14</v>
@@ -16131,13 +16242,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="E19" s="57" t="s">
         <v>29</v>
@@ -16149,13 +16260,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="E20" s="57" t="s">
         <v>14</v>
@@ -16167,13 +16278,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C21" s="56" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E21" s="57" t="s">
         <v>29</v>
@@ -16185,13 +16296,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="E22" s="57" t="s">
         <v>29</v>
@@ -16203,13 +16314,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E23" s="57" t="s">
         <v>29</v>
@@ -16221,13 +16332,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C24" s="56" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="E24" s="57" t="s">
         <v>14</v>
@@ -16239,13 +16350,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="E25" s="57" t="s">
         <v>14</v>
@@ -16257,13 +16368,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="E26" s="57" t="s">
         <v>29</v>
@@ -16275,13 +16386,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C27" s="56" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="E27" s="57" t="s">
         <v>14</v>
@@ -16293,16 +16404,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E28" s="57" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16311,16 +16422,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="E29" s="57" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16329,13 +16440,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="E30" s="57" t="s">
         <v>29</v>
@@ -16347,13 +16458,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="E31" s="57" t="s">
         <v>29</v>
@@ -16365,13 +16476,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="E32" s="57" t="s">
         <v>29</v>
@@ -16383,13 +16494,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="E33" s="57" t="s">
         <v>29</v>
@@ -16401,13 +16512,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C34" s="56" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="E34" s="57" t="s">
         <v>29</v>
@@ -16419,13 +16530,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="E35" s="57" t="s">
         <v>14</v>
@@ -16437,13 +16548,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C36" s="56" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="E36" s="57" t="s">
         <v>29</v>
@@ -16455,13 +16566,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C37" s="56" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="E37" s="57" t="s">
         <v>29</v>
@@ -16473,13 +16584,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C38" s="56" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="E38" s="57" t="s">
         <v>29</v>
@@ -16491,13 +16602,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C39" s="56" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="D39" s="56" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="E39" s="57" t="s">
         <v>29</v>
@@ -16509,13 +16620,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C40" s="56" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="D40" s="56" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="E40" s="57" t="s">
         <v>29</v>
@@ -16527,13 +16638,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C41" s="56" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="D41" s="56" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="E41" s="57" t="s">
         <v>29</v>
@@ -16545,13 +16656,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="56" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C42" s="56" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="D42" s="56" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="E42" s="57" t="s">
         <v>29</v>
@@ -16563,16 +16674,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="56" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C43" s="56" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="D43" s="56" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="E43" s="57" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16581,13 +16692,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="56" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C44" s="56" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="D44" s="56" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="E44" s="57" t="s">
         <v>14</v>
@@ -16599,13 +16710,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="56" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C45" s="56" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="D45" s="56" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="E45" s="57" t="s">
         <v>14</v>
@@ -16617,13 +16728,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="56" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C46" s="56" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="D46" s="56" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="E46" s="57" t="s">
         <v>14</v>
@@ -16635,13 +16746,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="56" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="C47" s="56" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="D47" s="56" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="E47" s="57" t="s">
         <v>29</v>
@@ -16653,13 +16764,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="56" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="C48" s="56" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="D48" s="56" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E48" s="57" t="s">
         <v>29</v>
@@ -16671,13 +16782,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="56" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="C49" s="56" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="D49" s="56" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="E49" s="57" t="s">
         <v>29</v>
@@ -16686,13 +16797,13 @@
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>3</v>
@@ -16704,13 +16815,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>14</v>
@@ -16722,13 +16833,13 @@
         <v>2</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>14</v>
@@ -16740,13 +16851,13 @@
         <v>3</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>29</v>
@@ -16758,13 +16869,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>14</v>
@@ -16776,13 +16887,13 @@
         <v>5</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>29</v>
@@ -16794,13 +16905,13 @@
         <v>6</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>29</v>
@@ -16812,13 +16923,13 @@
         <v>7</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>29</v>
@@ -16830,13 +16941,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>14</v>
@@ -16848,13 +16959,13 @@
         <v>9</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>29</v>
@@ -16866,13 +16977,13 @@
         <v>10</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>29</v>
@@ -16884,13 +16995,13 @@
         <v>11</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>14</v>
@@ -16902,13 +17013,13 @@
         <v>12</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>14</v>
@@ -16920,13 +17031,13 @@
         <v>13</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>14</v>
@@ -16938,13 +17049,13 @@
         <v>14</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>14</v>
@@ -16956,13 +17067,13 @@
         <v>15</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>29</v>
@@ -16974,13 +17085,13 @@
         <v>16</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>14</v>
@@ -16992,13 +17103,13 @@
         <v>17</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>29</v>
@@ -17010,13 +17121,13 @@
         <v>18</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>29</v>
@@ -17028,13 +17139,13 @@
         <v>19</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>29</v>
@@ -17046,13 +17157,13 @@
         <v>20</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>14</v>
@@ -17064,13 +17175,13 @@
         <v>21</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>14</v>
@@ -17082,13 +17193,13 @@
         <v>22</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>14</v>
@@ -17100,13 +17211,13 @@
         <v>23</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>29</v>
@@ -17118,13 +17229,13 @@
         <v>24</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>14</v>
@@ -17136,16 +17247,16 @@
         <v>25</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17154,16 +17265,16 @@
         <v>26</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17172,13 +17283,13 @@
         <v>27</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>29</v>
@@ -17190,13 +17301,13 @@
         <v>28</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>29</v>
@@ -17208,13 +17319,13 @@
         <v>29</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>29</v>
@@ -17226,13 +17337,13 @@
         <v>30</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>29</v>
@@ -17244,13 +17355,13 @@
         <v>31</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>29</v>
@@ -17262,13 +17373,13 @@
         <v>32</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>29</v>
@@ -17280,16 +17391,16 @@
         <v>33</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17298,13 +17409,13 @@
         <v>34</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>29</v>
@@ -17316,13 +17427,13 @@
         <v>35</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>14</v>
@@ -17334,13 +17445,13 @@
         <v>36</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>29</v>
@@ -17352,13 +17463,13 @@
         <v>37</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>29</v>
@@ -17370,13 +17481,13 @@
         <v>38</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>29</v>
@@ -17388,13 +17499,13 @@
         <v>39</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>29</v>
@@ -17406,13 +17517,13 @@
         <v>40</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>29</v>
@@ -17424,13 +17535,13 @@
         <v>41</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>29</v>
@@ -17442,13 +17553,13 @@
         <v>42</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>29</v>
@@ -17460,13 +17571,13 @@
         <v>43</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>29</v>
@@ -17478,13 +17589,13 @@
         <v>44</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>29</v>
@@ -17496,16 +17607,16 @@
         <v>45</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>29</v>
@@ -17517,16 +17628,16 @@
         <v>46</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>29</v>
@@ -17538,16 +17649,16 @@
         <v>47</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>29</v>
@@ -17559,19 +17670,19 @@
         <v>48</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17580,16 +17691,16 @@
         <v>49</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>14</v>
@@ -17601,16 +17712,16 @@
         <v>50</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>14</v>
@@ -17621,22 +17732,22 @@
         <v>1</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="H106" s="9"/>
     </row>
@@ -17646,22 +17757,22 @@
         <v>1</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17670,19 +17781,19 @@
         <v>2</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17691,19 +17802,19 @@
         <v>3</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17712,19 +17823,19 @@
         <v>4</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17733,22 +17844,22 @@
         <v>5</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17757,22 +17868,22 @@
         <v>6</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17781,19 +17892,19 @@
         <v>7</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17802,22 +17913,22 @@
         <v>8</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17826,19 +17937,19 @@
         <v>9</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17847,19 +17958,19 @@
         <v>10</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17868,22 +17979,22 @@
         <v>11</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17892,19 +18003,19 @@
         <v>12</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17913,19 +18024,19 @@
         <v>13</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17934,22 +18045,22 @@
         <v>14</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17958,19 +18069,19 @@
         <v>15</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17979,19 +18090,19 @@
         <v>16</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18000,22 +18111,22 @@
         <v>17</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>48</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18024,19 +18135,19 @@
         <v>18</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18045,19 +18156,19 @@
         <v>19</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18066,28 +18177,28 @@
         <v>20</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18096,19 +18207,19 @@
         <v>21</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18117,19 +18228,19 @@
         <v>22</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18138,25 +18249,25 @@
         <v>23</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>14</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18165,19 +18276,19 @@
         <v>24</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18186,19 +18297,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18207,22 +18318,22 @@
         <v>26</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18231,19 +18342,19 @@
         <v>27</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18252,19 +18363,19 @@
         <v>28</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18273,22 +18384,22 @@
         <v>29</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18297,19 +18408,19 @@
         <v>30</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18318,19 +18429,19 @@
         <v>31</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18339,19 +18450,19 @@
         <v>32</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18360,28 +18471,28 @@
         <v>33</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>29</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18390,19 +18501,19 @@
         <v>34</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18411,19 +18522,19 @@
         <v>35</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18432,25 +18543,25 @@
         <v>36</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18459,19 +18570,19 @@
         <v>37</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18480,19 +18591,19 @@
         <v>38</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18501,31 +18612,31 @@
         <v>39</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18534,19 +18645,19 @@
         <v>40</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18555,19 +18666,19 @@
         <v>41</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18576,19 +18687,19 @@
         <v>42</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18597,19 +18708,19 @@
         <v>43</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18618,22 +18729,22 @@
         <v>44</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18642,19 +18753,19 @@
         <v>45</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18663,19 +18774,19 @@
         <v>46</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18684,22 +18795,22 @@
         <v>47</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18708,19 +18819,19 @@
         <v>48</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18729,19 +18840,19 @@
         <v>49</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18750,22 +18861,22 @@
         <v>50</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18774,19 +18885,19 @@
         <v>51</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18795,19 +18906,19 @@
         <v>52</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18816,25 +18927,25 @@
         <v>53</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18843,19 +18954,19 @@
         <v>54</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18864,22 +18975,22 @@
         <v>55</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18888,19 +18999,19 @@
         <v>56</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18909,22 +19020,22 @@
         <v>57</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18933,22 +19044,22 @@
         <v>58</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18957,19 +19068,19 @@
         <v>59</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
   </sheetData>
@@ -19011,28 +19122,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="D1" s="42" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19041,10 +19152,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="D2" s="59" t="n">
         <v>45849</v>
@@ -19080,10 +19191,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="D3" s="59" t="n">
         <v>45849</v>
@@ -19119,10 +19230,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="D4" s="59" t="n">
         <v>45849</v>
@@ -19158,10 +19269,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="D5" s="61" t="n">
         <v>45849</v>
@@ -19197,10 +19308,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="D6" s="61" t="n">
         <v>45849</v>
@@ -19236,10 +19347,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="D7" s="61" t="n">
         <v>45849</v>
@@ -19275,10 +19386,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="D8" s="61" t="n">
         <v>45849</v>
@@ -19314,10 +19425,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="D9" s="62" t="n">
         <v>45850</v>
@@ -19353,10 +19464,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="D10" s="62" t="n">
         <v>45850</v>
@@ -19392,10 +19503,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="D11" s="62" t="n">
         <v>45850</v>
@@ -19431,7 +19542,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="62" t="n">
@@ -19468,10 +19579,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="D13" s="62"/>
       <c r="E13" s="17" t="n">
@@ -19505,10 +19616,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="D14" s="62" t="n">
         <v>45850</v>
@@ -19544,10 +19655,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="D15" s="62" t="n">
         <v>45850</v>
@@ -19583,10 +19694,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="D16" s="62" t="n">
         <v>45850</v>
@@ -19622,10 +19733,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="D17" s="62"/>
       <c r="E17" s="17" t="n">
@@ -19659,10 +19770,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="D18" s="62"/>
       <c r="E18" s="17" t="n">
@@ -19696,10 +19807,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
       <c r="D19" s="62"/>
       <c r="E19" s="17" t="n">
@@ -19733,10 +19844,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="D20" s="62"/>
       <c r="E20" s="17" t="n">
@@ -19770,10 +19881,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="D21" s="62"/>
       <c r="E21" s="17" t="n">
@@ -19807,10 +19918,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="D22" s="62"/>
       <c r="E22" s="17" t="n">
@@ -19844,10 +19955,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="D23" s="62"/>
       <c r="E23" s="17" t="n">
@@ -19881,10 +19992,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="D24" s="62"/>
       <c r="E24" s="17" t="n">
@@ -19918,10 +20029,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="D25" s="62"/>
       <c r="E25" s="17" t="n">
@@ -19955,10 +20066,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="D26" s="62"/>
       <c r="E26" s="17" t="n">
@@ -19992,10 +20103,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="D27" s="62"/>
       <c r="E27" s="17" t="n">
@@ -20029,10 +20140,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="D28" s="62"/>
       <c r="E28" s="17" t="n">
@@ -20066,10 +20177,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="D29" s="62"/>
       <c r="E29" s="17" t="n">
@@ -20103,10 +20214,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="D30" s="62"/>
       <c r="E30" s="17" t="n">
@@ -20140,10 +20251,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="D31" s="62"/>
       <c r="E31" s="17" t="n">
@@ -20177,10 +20288,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="D32" s="62"/>
       <c r="E32" s="17" t="n">
@@ -20214,10 +20325,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="D33" s="62"/>
       <c r="E33" s="17" t="n">
@@ -20251,10 +20362,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="D34" s="62"/>
       <c r="E34" s="17" t="n">
@@ -20288,10 +20399,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="D35" s="62"/>
       <c r="E35" s="17" t="n">
@@ -20325,10 +20436,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="D36" s="62"/>
       <c r="E36" s="17" t="n">
@@ -20362,10 +20473,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="D37" s="62"/>
       <c r="E37" s="17" t="n">
@@ -20402,7 +20513,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="D38" s="62"/>
       <c r="E38" s="17" t="n">
@@ -20436,10 +20547,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="D39" s="62"/>
       <c r="E39" s="17" t="n">
@@ -20473,10 +20584,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="D40" s="62"/>
       <c r="E40" s="17" t="n">
@@ -20510,10 +20621,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="D41" s="62"/>
       <c r="E41" s="17" t="n">
@@ -20547,7 +20658,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="62"/>
@@ -20582,7 +20693,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="62"/>
@@ -20617,7 +20728,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="62"/>
@@ -20652,10 +20763,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="17" t="n">
@@ -20689,10 +20800,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="D46" s="62"/>
       <c r="E46" s="17" t="n">
@@ -20726,10 +20837,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="D47" s="62"/>
       <c r="E47" s="17" t="n">
@@ -20763,10 +20874,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="D48" s="62"/>
       <c r="E48" s="17" t="n">
@@ -20800,10 +20911,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="D49" s="62"/>
       <c r="E49" s="17" t="n">
@@ -20837,10 +20948,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="D50" s="62"/>
       <c r="E50" s="17" t="n">
@@ -20874,10 +20985,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="D51" s="62"/>
       <c r="E51" s="17" t="n">
@@ -20911,10 +21022,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="D52" s="62"/>
       <c r="E52" s="17" t="n">
@@ -20948,10 +21059,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="D53" s="62"/>
       <c r="E53" s="17" t="n">
@@ -20985,10 +21096,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>807</v>
+        <v>816</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="D54" s="62"/>
       <c r="E54" s="17" t="n">
@@ -21022,10 +21133,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="D55" s="62"/>
       <c r="E55" s="17" t="n">
@@ -21059,10 +21170,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="D56" s="62"/>
       <c r="E56" s="17" t="n">
@@ -21096,10 +21207,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D57" s="62"/>
       <c r="E57" s="17" t="n">
@@ -21133,10 +21244,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="D58" s="62"/>
       <c r="E58" s="17" t="n">
@@ -21170,10 +21281,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="D59" s="62"/>
       <c r="E59" s="17" t="n">
@@ -21207,7 +21318,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="C60" s="16"/>
       <c r="D60" s="62"/>
@@ -21242,10 +21353,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="D61" s="62"/>
       <c r="E61" s="17" t="n">
@@ -21279,10 +21390,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>823</v>
+        <v>832</v>
       </c>
       <c r="D62" s="62"/>
       <c r="E62" s="17" t="n">
@@ -21316,10 +21427,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="D63" s="62"/>
       <c r="E63" s="17" t="n">
@@ -21353,10 +21464,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>827</v>
+        <v>836</v>
       </c>
       <c r="D64" s="62"/>
       <c r="E64" s="17" t="n">
@@ -21390,10 +21501,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>828</v>
+        <v>837</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>829</v>
+        <v>838</v>
       </c>
       <c r="D65" s="62"/>
       <c r="E65" s="17" t="n">
@@ -21427,10 +21538,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>830</v>
+        <v>839</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="D66" s="62"/>
       <c r="E66" s="17" t="n">
@@ -21464,10 +21575,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="65" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="D67" s="62"/>
       <c r="E67" s="17"/>
@@ -21483,10 +21594,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="65" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="D68" s="62"/>
       <c r="E68" s="17"/>
@@ -21502,10 +21613,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="65" t="s">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="D69" s="62"/>
       <c r="E69" s="17"/>
@@ -21521,10 +21632,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="D70" s="62"/>
       <c r="E70" s="17"/>
@@ -21540,10 +21651,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="65" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="D71" s="62"/>
       <c r="E71" s="17"/>
@@ -25861,10 +25972,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="68" t="s">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
@@ -25876,10 +25987,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="70" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="C2" s="71"/>
       <c r="D2" s="71"/>
@@ -25891,10 +26002,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="70" t="s">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="C3" s="71"/>
       <c r="D3" s="71"/>
@@ -25906,10 +26017,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="70" t="s">
-        <v>848</v>
+        <v>857</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
@@ -25921,10 +26032,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="70" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
@@ -25936,10 +26047,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="70" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
@@ -25951,10 +26062,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="70" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>855</v>
+        <v>864</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
@@ -25966,16 +26077,16 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="70" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>857</v>
+        <v>866</v>
       </c>
       <c r="C8" s="71"/>
       <c r="D8" s="71"/>
       <c r="E8" s="71"/>
       <c r="F8" s="11" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="G8" s="69"/>
       <c r="H8" s="69"/>
@@ -25994,7 +26105,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="C10" s="42" t="s">
         <v>4</v>
@@ -26015,7 +26126,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="72" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26024,7 +26135,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="73" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="C11" s="17" t="n">
         <v>45855</v>
@@ -26060,7 +26171,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="74" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="C12" s="17" t="n">
         <v>45855</v>
@@ -26097,7 +26208,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="74" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="C13" s="75"/>
       <c r="D13" s="17"/>

--- a/trackers/LCrev.xlsx
+++ b/trackers/LCrev.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="1002">
   <si>
     <t xml:space="preserve">DSA-Notes</t>
   </si>
@@ -228,6 +228,24 @@
   </si>
   <si>
     <t xml:space="preserve">Mds &amp; map, if new large element found pop, if not found then it will be in stacl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best-time-to-buy-and-sell-stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sliding Window/2 Pointer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minPrice, MaxProfit keep tracking from left to right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">longest-substring-without-repeating-characters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sliding Window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Grow right; on repeat, **jump left** past the previous index of that char; track best window length.</t>
   </si>
   <si>
     <t xml:space="preserve">Problem </t>
@@ -1804,9 +1822,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cycle detection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sliding Window</t>
   </si>
   <si>
     <t xml:space="preserve">Maintain a section of array for subarrays/substrings with constraints</t>
@@ -2527,9 +2542,6 @@
   </si>
   <si>
     <t xml:space="preserve">anagrams will have same hashValue. Create a Hashfunction such that all elements will have same hash value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">longest-substring-without-repeating-characters</t>
   </si>
   <si>
     <t xml:space="preserve">Do sliding window, Keep track of the LastOccured Index. &amp; </t>
@@ -4087,7 +4099,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="28.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="31.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="57.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="8" style="2" width="11.53"/>
@@ -4857,34 +4869,94 @@
         <f aca="false">ROW()-2</f>
         <v>17</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="31"/>
+      <c r="B19" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>45889</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <f aca="false">D19+2</f>
+        <v>45891</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <f aca="false">D19+7</f>
+        <v>45896</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <f aca="false">D19+21</f>
+        <v>45910</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <f aca="false">D19+45</f>
+        <v>45934</v>
+      </c>
+      <c r="L19" s="18" t="n">
+        <f aca="false">D19+60</f>
+        <v>45949</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="31"/>
+      <c r="A20" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>18</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>45889</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <f aca="false">D20+2</f>
+        <v>45891</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <f aca="false">D20+7</f>
+        <v>45896</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <f aca="false">D20+21</f>
+        <v>45910</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <f aca="false">D20+45</f>
+        <v>45934</v>
+      </c>
+      <c r="L20" s="18" t="n">
+        <f aca="false">D20+60</f>
+        <v>45949</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32"/>
+      <c r="A21" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>19</v>
+      </c>
       <c r="B21" s="11"/>
       <c r="C21" s="12"/>
       <c r="D21" s="17"/>
@@ -4898,7 +4970,10 @@
       <c r="L21" s="31"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32"/>
+      <c r="A22" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>20</v>
+      </c>
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="17"/>
@@ -4912,7 +4987,10 @@
       <c r="L22" s="31"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32"/>
+      <c r="A23" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>21</v>
+      </c>
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
       <c r="D23" s="17"/>
@@ -4926,7 +5004,10 @@
       <c r="L23" s="31"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32"/>
+      <c r="A24" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>22</v>
+      </c>
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
       <c r="D24" s="17"/>
@@ -4940,7 +5021,10 @@
       <c r="L24" s="31"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32"/>
+      <c r="A25" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>23</v>
+      </c>
       <c r="B25" s="11"/>
       <c r="C25" s="12"/>
       <c r="D25" s="17"/>
@@ -4954,7 +5038,10 @@
       <c r="L25" s="31"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32"/>
+      <c r="A26" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>24</v>
+      </c>
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
       <c r="D26" s="17"/>
@@ -4968,7 +5055,10 @@
       <c r="L26" s="31"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32"/>
+      <c r="A27" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>25</v>
+      </c>
       <c r="B27" s="11"/>
       <c r="C27" s="12"/>
       <c r="D27" s="17"/>
@@ -4982,7 +5072,10 @@
       <c r="L27" s="31"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32"/>
+      <c r="A28" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>26</v>
+      </c>
       <c r="B28" s="11"/>
       <c r="C28" s="12"/>
       <c r="D28" s="17"/>
@@ -4996,7 +5089,10 @@
       <c r="L28" s="31"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32"/>
+      <c r="A29" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>27</v>
+      </c>
       <c r="B29" s="11"/>
       <c r="C29" s="12"/>
       <c r="D29" s="17"/>
@@ -5010,7 +5106,10 @@
       <c r="L29" s="31"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32"/>
+      <c r="A30" s="26" t="n">
+        <f aca="false">ROW()-2</f>
+        <v>28</v>
+      </c>
       <c r="B30" s="11"/>
       <c r="C30" s="12"/>
       <c r="D30" s="17"/>
@@ -8869,6 +8968,8 @@
     <hyperlink ref="B16" r:id="rId15" display="minimum-add-to-make-parentheses-valid"/>
     <hyperlink ref="B17" r:id="rId16" display="implement-queue-using-stacks"/>
     <hyperlink ref="B18" r:id="rId17" display="next-greater-element-i"/>
+    <hyperlink ref="B19" r:id="rId18" display="best-time-to-buy-and-sell-stock"/>
+    <hyperlink ref="B20" r:id="rId19" display="longest-substring-without-repeating-characters"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -8894,167 +8995,167 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="77" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="77" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="77" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="77" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="77" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="77" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="77" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="77" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="77" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="77" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="77" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="77" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="77" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="77" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="77" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="77" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="77" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="77" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="77" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="77" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="77" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="77" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="77" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="77" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="77" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="77" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="77" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="77" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -9150,94 +9251,94 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="78" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B1" s="79" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C1" s="79" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D2" s="80" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D3" s="80" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="D4" s="80" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9246,40 +9347,40 @@
     </row>
     <row r="13" customFormat="false" ht="35.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="83" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B13" s="83"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9288,211 +9389,211 @@
     </row>
     <row r="19" customFormat="false" ht="19.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="83" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B19" s="83"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="84" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="B20" s="84"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="84" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B21" s="84"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="84" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B22" s="84"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="84" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B23" s="84"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="51" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="85" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="85" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="51" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="85" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="85" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="85" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="85" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="85" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="85" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="85" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="85" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="85" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="85" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="24" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="24" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
   </sheetData>
@@ -9537,7 +9638,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9546,10 +9647,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9558,10 +9659,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9570,10 +9671,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9582,10 +9683,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9594,10 +9695,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9606,10 +9707,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9618,10 +9719,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9630,10 +9731,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9642,7 +9743,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="C10" s="48"/>
     </row>
@@ -9652,7 +9753,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C11" s="48"/>
     </row>
@@ -9662,7 +9763,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C12" s="48"/>
     </row>
@@ -9672,7 +9773,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C13" s="48"/>
     </row>
@@ -9911,12 +10012,12 @@
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="86" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
@@ -9948,10 +10049,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>3</v>
@@ -9963,10 +10064,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>14</v>
@@ -9981,7 +10082,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>14</v>
@@ -9996,7 +10097,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>14</v>
@@ -10011,7 +10112,7 @@
         <v>28</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>29</v>
@@ -10026,7 +10127,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>14</v>
@@ -12744,36 +12845,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B2" s="37" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12782,13 +12883,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12797,13 +12898,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12812,13 +12913,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12827,13 +12928,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12842,13 +12943,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12857,13 +12958,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12871,19 +12972,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B10" s="37" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12892,13 +12993,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12907,13 +13008,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12922,13 +13023,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12937,13 +13038,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12952,13 +13053,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12967,13 +13068,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12981,19 +13082,19 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B18" s="37" t="n">
         <v>15</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13002,13 +13103,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13017,13 +13118,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13032,13 +13133,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13047,13 +13148,13 @@
         <v>19</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13062,13 +13163,13 @@
         <v>20</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13077,13 +13178,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13091,19 +13192,19 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="36" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B26" s="37" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13112,13 +13213,13 @@
         <v>23</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13127,13 +13228,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13142,13 +13243,13 @@
         <v>25</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13157,13 +13258,13 @@
         <v>26</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13172,13 +13273,13 @@
         <v>27</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13187,13 +13288,13 @@
         <v>28</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13202,13 +13303,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13217,13 +13318,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13231,7 +13332,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -13244,13 +13345,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
@@ -13260,13 +13361,13 @@
         <v>3</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
@@ -13484,7 +13585,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -13497,13 +13598,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -13514,13 +13615,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -13531,13 +13632,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -13548,13 +13649,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -13565,13 +13666,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -13582,13 +13683,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -13599,13 +13700,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -13616,13 +13717,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -13633,13 +13734,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -13650,13 +13751,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -13667,13 +13768,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -13684,13 +13785,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -13701,13 +13802,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -13718,13 +13819,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -13735,13 +13836,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -13752,13 +13853,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -13769,13 +13870,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -13786,13 +13887,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -13803,13 +13904,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -13820,13 +13921,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -13837,13 +13938,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -13854,13 +13955,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -13920,22 +14021,22 @@
         <v>4</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="H29" s="42" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13944,7 +14045,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>45729</v>
@@ -13980,7 +14081,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>45729</v>
@@ -14016,7 +14117,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="44" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>45729</v>
@@ -14052,7 +14153,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>45729</v>
@@ -14088,7 +14189,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C34" s="25" t="n">
         <v>45729</v>
@@ -14124,7 +14225,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C35" s="25" t="n">
         <v>45729</v>
@@ -14160,7 +14261,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C36" s="25" t="n">
         <v>45729</v>
@@ -14196,7 +14297,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C37" s="25" t="n">
         <v>45729</v>
@@ -14232,7 +14333,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C38" s="25" t="n">
         <v>45729</v>
@@ -14268,7 +14369,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C39" s="25" t="n">
         <v>45729</v>
@@ -14304,7 +14405,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C40" s="25" t="n">
         <v>45729</v>
@@ -14340,7 +14441,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C41" s="25" t="n">
         <v>45729</v>
@@ -14376,7 +14477,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C42" s="25" t="n">
         <v>45729</v>
@@ -14412,7 +14513,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C43" s="25" t="n">
         <v>45729</v>
@@ -14448,7 +14549,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="46" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C44" s="25" t="n">
         <v>45729</v>
@@ -14484,7 +14585,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="46" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C45" s="25" t="n">
         <v>45729</v>
@@ -14520,7 +14621,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="46" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C46" s="25" t="n">
         <v>45729</v>
@@ -14556,7 +14657,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="46" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C47" s="25" t="n">
         <v>45729</v>
@@ -14592,7 +14693,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="46" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C48" s="25" t="n">
         <v>45729</v>
@@ -14628,7 +14729,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="46" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C49" s="25" t="n">
         <v>45729</v>
@@ -14664,7 +14765,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C50" s="25" t="n">
         <v>45729</v>
@@ -14700,7 +14801,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C51" s="25" t="n">
         <v>45729</v>
@@ -14736,7 +14837,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="46" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C52" s="25" t="n">
         <v>45729</v>
@@ -14772,7 +14873,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="46" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C53" s="25" t="n">
         <v>45729</v>
@@ -15048,7 +15149,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q1" s="49" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="R1" s="49"/>
       <c r="S1" s="49"/>
@@ -15056,119 +15157,119 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q2" s="35" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="R2" s="35" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="S2" s="35" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="T2" s="35" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q3" s="15" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q4" s="15" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="15" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q6" s="15" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="S6" s="15" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="T6" s="15" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q7" s="15" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="S7" s="15" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q8" s="15" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q9" s="15" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="S9" s="15" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q12" s="50" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="R12" s="50"/>
       <c r="S12" s="50"/>
@@ -15176,119 +15277,119 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q13" s="51" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="R13" s="51" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="S13" s="51" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="T13" s="51" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q14" s="24" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q15" s="24" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="T15" s="24" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q16" s="24" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="T16" s="24" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q17" s="24" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="T17" s="24" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q18" s="24" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="T18" s="24" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q19" s="24" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="R19" s="24" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="T19" s="24" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q20" s="24" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="R20" s="24" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="T20" s="24" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q23" s="50" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="R23" s="50"/>
       <c r="S23" s="50"/>
@@ -15296,119 +15397,119 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q24" s="51" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="R24" s="51" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="S24" s="51" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="T24" s="51" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q25" s="24" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="R25" s="24" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="S25" s="24" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="T25" s="24" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q26" s="24" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="S26" s="24" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="T26" s="24" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q27" s="24" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="R27" s="24" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="S27" s="24" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="T27" s="24" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q28" s="24" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="S28" s="24" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="T28" s="24" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q29" s="24" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="T29" s="24" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q30" s="24" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="R30" s="24" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="S30" s="24" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="T30" s="24" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q31" s="24" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="R31" s="24" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="S31" s="24" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="T31" s="24" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q33" s="50" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="R33" s="50"/>
       <c r="S33" s="50"/>
@@ -15416,154 +15517,154 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q34" s="51" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="R34" s="51" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="S34" s="51" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="T34" s="51" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q35" s="24" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="R35" s="24" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="S35" s="24" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="T35" s="24" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q36" s="24" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="R36" s="24" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="S36" s="24" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="T36" s="24" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q37" s="24" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="R37" s="24" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="S37" s="24" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="T37" s="24" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q38" s="24" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="R38" s="24" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="S38" s="24" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="T38" s="24" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q39" s="24" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="R39" s="24" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="S39" s="24" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="T39" s="24" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q40" s="24" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="R40" s="24" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="S40" s="24" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="T40" s="24" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q41" s="24" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="R41" s="24" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="S41" s="24" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="T41" s="24" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q44" s="52" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="R44" s="52"/>
       <c r="S44" s="52"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q45" s="51" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="R45" s="51" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="S45" s="51" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q46" s="24" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="R46" s="24" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S46" s="24" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q47" s="24" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="R47" s="24" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="S47" s="24" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -15600,291 +15701,291 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="53" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="54" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="54" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="54" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="54" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="54" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="54" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="53" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="54" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D13" s="54" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="54" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B14" s="54" t="s">
+        <v>417</v>
+      </c>
+      <c r="C14" s="54" t="s">
         <v>411</v>
       </c>
-      <c r="C14" s="54" t="s">
-        <v>405</v>
-      </c>
       <c r="D14" s="54" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C15" s="54" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D15" s="54" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D16" s="54" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="54" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D17" s="54" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="55" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="35" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C23" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C24" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C26" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -15918,13 +16019,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -15936,13 +16037,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E2" s="57" t="s">
         <v>14</v>
@@ -15954,13 +16055,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E3" s="57" t="s">
         <v>14</v>
@@ -15972,13 +16073,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>29</v>
@@ -15990,13 +16091,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E5" s="57" t="s">
         <v>14</v>
@@ -16008,13 +16109,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>29</v>
@@ -16026,13 +16127,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>29</v>
@@ -16044,13 +16145,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>29</v>
@@ -16062,13 +16163,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="E9" s="57" t="s">
         <v>29</v>
@@ -16080,13 +16181,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E10" s="57" t="s">
         <v>14</v>
@@ -16098,13 +16199,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E11" s="57" t="s">
         <v>29</v>
@@ -16116,13 +16217,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E12" s="57" t="s">
         <v>29</v>
@@ -16134,13 +16235,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C13" s="56" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E13" s="57" t="s">
         <v>29</v>
@@ -16152,13 +16253,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E14" s="57" t="s">
         <v>14</v>
@@ -16170,13 +16271,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="E15" s="57" t="s">
         <v>14</v>
@@ -16188,13 +16289,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E16" s="57" t="s">
         <v>14</v>
@@ -16206,13 +16307,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E17" s="57" t="s">
         <v>14</v>
@@ -16224,13 +16325,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>14</v>
@@ -16242,13 +16343,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E19" s="57" t="s">
         <v>29</v>
@@ -16260,13 +16361,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E20" s="57" t="s">
         <v>14</v>
@@ -16278,13 +16379,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C21" s="56" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E21" s="57" t="s">
         <v>29</v>
@@ -16296,13 +16397,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="E22" s="57" t="s">
         <v>29</v>
@@ -16314,13 +16415,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E23" s="57" t="s">
         <v>29</v>
@@ -16332,13 +16433,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C24" s="56" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="E24" s="57" t="s">
         <v>14</v>
@@ -16350,13 +16451,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E25" s="57" t="s">
         <v>14</v>
@@ -16368,13 +16469,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E26" s="57" t="s">
         <v>29</v>
@@ -16386,13 +16487,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C27" s="56" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="E27" s="57" t="s">
         <v>14</v>
@@ -16404,16 +16505,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="E28" s="57" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16422,16 +16523,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="E29" s="57" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16440,13 +16541,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="E30" s="57" t="s">
         <v>29</v>
@@ -16458,13 +16559,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E31" s="57" t="s">
         <v>29</v>
@@ -16476,13 +16577,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="E32" s="57" t="s">
         <v>29</v>
@@ -16494,13 +16595,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="E33" s="57" t="s">
         <v>29</v>
@@ -16512,13 +16613,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C34" s="56" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E34" s="57" t="s">
         <v>29</v>
@@ -16530,13 +16631,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E35" s="57" t="s">
         <v>14</v>
@@ -16548,13 +16649,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C36" s="56" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E36" s="57" t="s">
         <v>29</v>
@@ -16566,13 +16667,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C37" s="56" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E37" s="57" t="s">
         <v>29</v>
@@ -16584,13 +16685,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C38" s="56" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E38" s="57" t="s">
         <v>29</v>
@@ -16602,13 +16703,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C39" s="56" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D39" s="56" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E39" s="57" t="s">
         <v>29</v>
@@ -16620,13 +16721,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C40" s="56" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D40" s="56" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="E40" s="57" t="s">
         <v>29</v>
@@ -16638,13 +16739,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C41" s="56" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D41" s="56" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E41" s="57" t="s">
         <v>29</v>
@@ -16656,13 +16757,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="56" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C42" s="56" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D42" s="56" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E42" s="57" t="s">
         <v>29</v>
@@ -16674,16 +16775,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="56" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C43" s="56" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D43" s="56" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="E43" s="57" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16692,13 +16793,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="56" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C44" s="56" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D44" s="56" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="E44" s="57" t="s">
         <v>14</v>
@@ -16710,13 +16811,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="56" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C45" s="56" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D45" s="56" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="E45" s="57" t="s">
         <v>14</v>
@@ -16728,13 +16829,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="56" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C46" s="56" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D46" s="56" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E46" s="57" t="s">
         <v>14</v>
@@ -16746,13 +16847,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="56" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C47" s="56" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D47" s="56" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E47" s="57" t="s">
         <v>29</v>
@@ -16764,13 +16865,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="56" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C48" s="56" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D48" s="56" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E48" s="57" t="s">
         <v>29</v>
@@ -16782,13 +16883,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="56" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C49" s="56" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D49" s="56" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E49" s="57" t="s">
         <v>29</v>
@@ -16797,13 +16898,13 @@
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>3</v>
@@ -16815,13 +16916,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>14</v>
@@ -16833,13 +16934,13 @@
         <v>2</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>14</v>
@@ -16851,13 +16952,13 @@
         <v>3</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>29</v>
@@ -16869,13 +16970,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>14</v>
@@ -16887,13 +16988,13 @@
         <v>5</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>29</v>
@@ -16905,13 +17006,13 @@
         <v>6</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>29</v>
@@ -16923,13 +17024,13 @@
         <v>7</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>29</v>
@@ -16941,13 +17042,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>14</v>
@@ -16959,13 +17060,13 @@
         <v>9</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>29</v>
@@ -16977,13 +17078,13 @@
         <v>10</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>29</v>
@@ -16995,13 +17096,13 @@
         <v>11</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>14</v>
@@ -17013,13 +17114,13 @@
         <v>12</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>14</v>
@@ -17031,13 +17132,13 @@
         <v>13</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>14</v>
@@ -17049,13 +17150,13 @@
         <v>14</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>14</v>
@@ -17067,13 +17168,13 @@
         <v>15</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>29</v>
@@ -17085,13 +17186,13 @@
         <v>16</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>14</v>
@@ -17103,13 +17204,13 @@
         <v>17</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>29</v>
@@ -17121,13 +17222,13 @@
         <v>18</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>29</v>
@@ -17139,13 +17240,13 @@
         <v>19</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>29</v>
@@ -17157,13 +17258,13 @@
         <v>20</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>14</v>
@@ -17175,13 +17276,13 @@
         <v>21</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>14</v>
@@ -17193,13 +17294,13 @@
         <v>22</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>14</v>
@@ -17211,13 +17312,13 @@
         <v>23</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>29</v>
@@ -17229,13 +17330,13 @@
         <v>24</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>14</v>
@@ -17247,16 +17348,16 @@
         <v>25</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17265,16 +17366,16 @@
         <v>26</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17283,13 +17384,13 @@
         <v>27</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>29</v>
@@ -17301,13 +17402,13 @@
         <v>28</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>29</v>
@@ -17319,13 +17420,13 @@
         <v>29</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>29</v>
@@ -17337,13 +17438,13 @@
         <v>30</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>29</v>
@@ -17355,13 +17456,13 @@
         <v>31</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>29</v>
@@ -17373,13 +17474,13 @@
         <v>32</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>29</v>
@@ -17391,16 +17492,16 @@
         <v>33</v>
       </c>
       <c r="B84" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="E84" s="8" t="s">
         <v>505</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17409,13 +17510,13 @@
         <v>34</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>29</v>
@@ -17427,13 +17528,13 @@
         <v>35</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>14</v>
@@ -17445,13 +17546,13 @@
         <v>36</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>29</v>
@@ -17463,13 +17564,13 @@
         <v>37</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>29</v>
@@ -17481,13 +17582,13 @@
         <v>38</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>29</v>
@@ -17499,13 +17600,13 @@
         <v>39</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>29</v>
@@ -17517,13 +17618,13 @@
         <v>40</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>29</v>
@@ -17535,13 +17636,13 @@
         <v>41</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>29</v>
@@ -17553,13 +17654,13 @@
         <v>42</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>29</v>
@@ -17571,13 +17672,13 @@
         <v>43</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>29</v>
@@ -17589,13 +17690,13 @@
         <v>44</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>29</v>
@@ -17607,16 +17708,16 @@
         <v>45</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>29</v>
@@ -17628,16 +17729,16 @@
         <v>46</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>29</v>
@@ -17649,16 +17750,16 @@
         <v>47</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>29</v>
@@ -17670,19 +17771,19 @@
         <v>48</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17691,16 +17792,16 @@
         <v>49</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>14</v>
@@ -17712,16 +17813,16 @@
         <v>50</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>14</v>
@@ -17732,22 +17833,22 @@
         <v>1</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="H106" s="9"/>
     </row>
@@ -17757,22 +17858,22 @@
         <v>1</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17781,19 +17882,19 @@
         <v>2</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17802,19 +17903,19 @@
         <v>3</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17823,19 +17924,19 @@
         <v>4</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17844,22 +17945,22 @@
         <v>5</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>583</v>
+        <v>68</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17868,22 +17969,22 @@
         <v>6</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>583</v>
+        <v>68</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17892,19 +17993,19 @@
         <v>7</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>583</v>
+        <v>68</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17913,22 +18014,22 @@
         <v>8</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17937,19 +18038,19 @@
         <v>9</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17958,19 +18059,19 @@
         <v>10</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17979,22 +18080,22 @@
         <v>11</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18003,19 +18104,19 @@
         <v>12</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18024,19 +18125,19 @@
         <v>13</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18045,22 +18146,22 @@
         <v>14</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18069,19 +18170,19 @@
         <v>15</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18090,19 +18191,19 @@
         <v>16</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18111,22 +18212,22 @@
         <v>17</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>48</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18135,19 +18236,19 @@
         <v>18</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18156,19 +18257,19 @@
         <v>19</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18177,28 +18278,28 @@
         <v>20</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18207,19 +18308,19 @@
         <v>21</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18228,19 +18329,19 @@
         <v>22</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18249,25 +18350,25 @@
         <v>23</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>14</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18276,19 +18377,19 @@
         <v>24</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18297,19 +18398,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18318,22 +18419,22 @@
         <v>26</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18342,19 +18443,19 @@
         <v>27</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18363,19 +18464,19 @@
         <v>28</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18384,22 +18485,22 @@
         <v>29</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18408,19 +18509,19 @@
         <v>30</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18429,19 +18530,19 @@
         <v>31</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18450,19 +18551,19 @@
         <v>32</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18471,28 +18572,28 @@
         <v>33</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>29</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18501,19 +18602,19 @@
         <v>34</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18522,19 +18623,19 @@
         <v>35</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18543,25 +18644,25 @@
         <v>36</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18570,19 +18671,19 @@
         <v>37</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18591,19 +18692,19 @@
         <v>38</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18612,31 +18713,31 @@
         <v>39</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18645,19 +18746,19 @@
         <v>40</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18666,19 +18767,19 @@
         <v>41</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18687,19 +18788,19 @@
         <v>42</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18708,19 +18809,19 @@
         <v>43</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18729,22 +18830,22 @@
         <v>44</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18753,19 +18854,19 @@
         <v>45</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18774,19 +18875,19 @@
         <v>46</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18795,22 +18896,22 @@
         <v>47</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18819,19 +18920,19 @@
         <v>48</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18840,19 +18941,19 @@
         <v>49</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18861,22 +18962,22 @@
         <v>50</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18885,19 +18986,19 @@
         <v>51</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18906,19 +19007,19 @@
         <v>52</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18927,25 +19028,25 @@
         <v>53</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18954,19 +19055,19 @@
         <v>54</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18975,22 +19076,22 @@
         <v>55</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18999,19 +19100,19 @@
         <v>56</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19020,22 +19121,22 @@
         <v>57</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19044,22 +19145,22 @@
         <v>58</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19068,19 +19169,19 @@
         <v>59</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -19122,28 +19223,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="D1" s="42" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19152,10 +19253,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="D2" s="59" t="n">
         <v>45849</v>
@@ -19191,10 +19292,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="D3" s="59" t="n">
         <v>45849</v>
@@ -19230,10 +19331,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="D4" s="59" t="n">
         <v>45849</v>
@@ -19269,10 +19370,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="D5" s="61" t="n">
         <v>45849</v>
@@ -19308,10 +19409,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="D6" s="61" t="n">
         <v>45849</v>
@@ -19347,10 +19448,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="D7" s="61" t="n">
         <v>45849</v>
@@ -19386,10 +19487,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="D8" s="61" t="n">
         <v>45849</v>
@@ -19425,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="D9" s="62" t="n">
         <v>45850</v>
@@ -19464,10 +19565,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="D10" s="62" t="n">
         <v>45850</v>
@@ -19503,10 +19604,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="D11" s="62" t="n">
         <v>45850</v>
@@ -19542,7 +19643,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="62" t="n">
@@ -19579,10 +19680,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D13" s="62"/>
       <c r="E13" s="17" t="n">
@@ -19616,10 +19717,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D14" s="62" t="n">
         <v>45850</v>
@@ -19655,10 +19756,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="D15" s="62" t="n">
         <v>45850</v>
@@ -19694,10 +19795,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D16" s="62" t="n">
         <v>45850</v>
@@ -19733,10 +19834,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="D17" s="62"/>
       <c r="E17" s="17" t="n">
@@ -19770,10 +19871,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="D18" s="62"/>
       <c r="E18" s="17" t="n">
@@ -19807,10 +19908,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="D19" s="62"/>
       <c r="E19" s="17" t="n">
@@ -19844,10 +19945,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="D20" s="62"/>
       <c r="E20" s="17" t="n">
@@ -19881,10 +19982,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="D21" s="62"/>
       <c r="E21" s="17" t="n">
@@ -19918,10 +20019,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="D22" s="62"/>
       <c r="E22" s="17" t="n">
@@ -19955,10 +20056,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="D23" s="62"/>
       <c r="E23" s="17" t="n">
@@ -19992,10 +20093,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="D24" s="62"/>
       <c r="E24" s="17" t="n">
@@ -20029,10 +20130,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="D25" s="62"/>
       <c r="E25" s="17" t="n">
@@ -20066,10 +20167,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="D26" s="62"/>
       <c r="E26" s="17" t="n">
@@ -20103,10 +20204,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="D27" s="62"/>
       <c r="E27" s="17" t="n">
@@ -20140,10 +20241,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>769</v>
+        <v>67</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="D28" s="62"/>
       <c r="E28" s="17" t="n">
@@ -20177,10 +20278,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D29" s="62"/>
       <c r="E29" s="17" t="n">
@@ -20214,10 +20315,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D30" s="62"/>
       <c r="E30" s="17" t="n">
@@ -20251,10 +20352,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D31" s="62"/>
       <c r="E31" s="17" t="n">
@@ -20288,10 +20389,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D32" s="62"/>
       <c r="E32" s="17" t="n">
@@ -20325,10 +20426,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D33" s="62"/>
       <c r="E33" s="17" t="n">
@@ -20362,10 +20463,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D34" s="62"/>
       <c r="E34" s="17" t="n">
@@ -20399,10 +20500,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D35" s="62"/>
       <c r="E35" s="17" t="n">
@@ -20436,10 +20537,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="D36" s="62"/>
       <c r="E36" s="17" t="n">
@@ -20473,10 +20574,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D37" s="62"/>
       <c r="E37" s="17" t="n">
@@ -20513,7 +20614,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="D38" s="62"/>
       <c r="E38" s="17" t="n">
@@ -20547,10 +20648,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="D39" s="62"/>
       <c r="E39" s="17" t="n">
@@ -20584,10 +20685,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D40" s="62"/>
       <c r="E40" s="17" t="n">
@@ -20621,10 +20722,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="D41" s="62"/>
       <c r="E41" s="17" t="n">
@@ -20658,7 +20759,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="62"/>
@@ -20693,7 +20794,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="62"/>
@@ -20728,7 +20829,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="62"/>
@@ -20763,10 +20864,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="17" t="n">
@@ -20800,10 +20901,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D46" s="62"/>
       <c r="E46" s="17" t="n">
@@ -20837,10 +20938,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="D47" s="62"/>
       <c r="E47" s="17" t="n">
@@ -20874,10 +20975,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="D48" s="62"/>
       <c r="E48" s="17" t="n">
@@ -20911,10 +21012,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="D49" s="62"/>
       <c r="E49" s="17" t="n">
@@ -20948,10 +21049,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D50" s="62"/>
       <c r="E50" s="17" t="n">
@@ -20985,10 +21086,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D51" s="62"/>
       <c r="E51" s="17" t="n">
@@ -21022,10 +21123,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="D52" s="62"/>
       <c r="E52" s="17" t="n">
@@ -21059,10 +21160,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D53" s="62"/>
       <c r="E53" s="17" t="n">
@@ -21096,10 +21197,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="D54" s="62"/>
       <c r="E54" s="17" t="n">
@@ -21133,10 +21234,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D55" s="62"/>
       <c r="E55" s="17" t="n">
@@ -21170,10 +21271,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="D56" s="62"/>
       <c r="E56" s="17" t="n">
@@ -21207,10 +21308,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D57" s="62"/>
       <c r="E57" s="17" t="n">
@@ -21244,10 +21345,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="D58" s="62"/>
       <c r="E58" s="17" t="n">
@@ -21281,10 +21382,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D59" s="62"/>
       <c r="E59" s="17" t="n">
@@ -21318,7 +21419,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C60" s="16"/>
       <c r="D60" s="62"/>
@@ -21353,10 +21454,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D61" s="62"/>
       <c r="E61" s="17" t="n">
@@ -21390,10 +21491,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="D62" s="62"/>
       <c r="E62" s="17" t="n">
@@ -21427,10 +21528,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D63" s="62"/>
       <c r="E63" s="17" t="n">
@@ -21464,10 +21565,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="D64" s="62"/>
       <c r="E64" s="17" t="n">
@@ -21501,10 +21602,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="D65" s="62"/>
       <c r="E65" s="17" t="n">
@@ -21538,10 +21639,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D66" s="62"/>
       <c r="E66" s="17" t="n">
@@ -21575,10 +21676,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="65" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D67" s="62"/>
       <c r="E67" s="17"/>
@@ -21594,10 +21695,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="65" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D68" s="62"/>
       <c r="E68" s="17"/>
@@ -21613,10 +21714,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="65" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="D69" s="62"/>
       <c r="E69" s="17"/>
@@ -21632,10 +21733,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D70" s="62"/>
       <c r="E70" s="17"/>
@@ -21651,10 +21752,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="65" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D71" s="62"/>
       <c r="E71" s="17"/>
@@ -25972,10 +26073,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="68" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
@@ -25987,10 +26088,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="70" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="C2" s="71"/>
       <c r="D2" s="71"/>
@@ -26002,10 +26103,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="70" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C3" s="71"/>
       <c r="D3" s="71"/>
@@ -26017,10 +26118,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="70" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
@@ -26032,10 +26133,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="70" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
@@ -26047,10 +26148,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="70" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
@@ -26062,10 +26163,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="70" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
@@ -26077,16 +26178,16 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="70" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="C8" s="71"/>
       <c r="D8" s="71"/>
       <c r="E8" s="71"/>
       <c r="F8" s="11" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="G8" s="69"/>
       <c r="H8" s="69"/>
@@ -26105,7 +26206,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C10" s="42" t="s">
         <v>4</v>
@@ -26126,7 +26227,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="72" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26135,7 +26236,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="73" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="C11" s="17" t="n">
         <v>45855</v>
@@ -26171,7 +26272,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="74" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C12" s="17" t="n">
         <v>45855</v>
@@ -26208,7 +26309,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="74" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="C13" s="75"/>
       <c r="D13" s="17"/>

--- a/trackers/LCrev.xlsx
+++ b/trackers/LCrev.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="1004">
   <si>
     <t xml:space="preserve">DSA-Notes</t>
   </si>
@@ -246,6 +246,12 @@
   </si>
   <si>
     <t xml:space="preserve">“Grow right; on repeat, **jump left** past the previous index of that char; track best window length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">longest-repeating-character-replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SubstringLength-MaxFreq&lt;=k for valid window</t>
   </si>
   <si>
     <t xml:space="preserve">Problem </t>
@@ -4336,7 +4342,7 @@
         <v>45928</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="n">
         <f aca="false">ROW()-2</f>
         <v>5</v>
@@ -4957,17 +4963,44 @@
         <f aca="false">ROW()-2</f>
         <v>19</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="31"/>
+      <c r="B21" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>45889</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <f aca="false">D21+2</f>
+        <v>45891</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <f aca="false">D21+7</f>
+        <v>45896</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <f aca="false">D21+21</f>
+        <v>45910</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <f aca="false">D21+45</f>
+        <v>45934</v>
+      </c>
+      <c r="L21" s="18" t="n">
+        <f aca="false">D21+60</f>
+        <v>45949</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="n">
@@ -8970,6 +9003,7 @@
     <hyperlink ref="B18" r:id="rId17" display="next-greater-element-i"/>
     <hyperlink ref="B19" r:id="rId18" display="best-time-to-buy-and-sell-stock"/>
     <hyperlink ref="B20" r:id="rId19" display="longest-substring-without-repeating-characters"/>
+    <hyperlink ref="B21" r:id="rId20" display="longest-repeating-character-replacement"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -8995,167 +9029,167 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="77" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="77" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="77" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="77" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="77" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="77" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="77" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="77" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="77" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="77" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="77" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="77" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="77" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="77" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="77" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="77" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="77" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="77" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="77" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="77" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="77" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="77" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="77" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="77" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="77" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="77" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="77" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="77" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="77" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="77" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
   </sheetData>
@@ -9251,94 +9285,94 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="78" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B1" s="79" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C1" s="79" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D2" s="80" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D3" s="80" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="D4" s="80" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9347,40 +9381,40 @@
     </row>
     <row r="13" customFormat="false" ht="35.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="83" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B13" s="83"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9389,211 +9423,211 @@
     </row>
     <row r="19" customFormat="false" ht="19.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="83" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B19" s="83"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="84" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B20" s="84"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="84" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B21" s="84"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="84" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B22" s="84"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="84" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B23" s="84"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="51" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="85" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="85" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="51" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="85" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="85" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="85" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="85" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="85" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="85" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="85" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="85" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="85" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="85" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="24" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="24" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
   </sheetData>
@@ -9638,7 +9672,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9647,10 +9681,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9659,10 +9693,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9671,10 +9705,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9683,10 +9717,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9695,10 +9729,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9707,10 +9741,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9719,10 +9753,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9731,10 +9765,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9743,7 +9777,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C10" s="48"/>
     </row>
@@ -9753,7 +9787,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C11" s="48"/>
     </row>
@@ -9763,7 +9797,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C12" s="48"/>
     </row>
@@ -9773,7 +9807,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C13" s="48"/>
     </row>
@@ -10012,12 +10046,12 @@
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="86" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
@@ -10049,10 +10083,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>3</v>
@@ -10064,10 +10098,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>14</v>
@@ -10082,7 +10116,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>14</v>
@@ -10097,7 +10131,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>14</v>
@@ -10112,7 +10146,7 @@
         <v>28</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>29</v>
@@ -10127,7 +10161,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>14</v>
@@ -12845,36 +12879,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="37" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12883,13 +12917,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12898,13 +12932,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12913,13 +12947,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12928,13 +12962,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12943,13 +12977,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12958,13 +12992,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12972,19 +13006,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B10" s="37" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12993,13 +13027,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13008,13 +13042,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13023,13 +13057,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13038,13 +13072,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13053,13 +13087,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13068,13 +13102,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13082,19 +13116,19 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B18" s="37" t="n">
         <v>15</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13103,13 +13137,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13118,13 +13152,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13133,13 +13167,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13148,13 +13182,13 @@
         <v>19</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13163,13 +13197,13 @@
         <v>20</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13178,13 +13212,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13192,19 +13226,19 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="36" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B26" s="37" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13213,13 +13247,13 @@
         <v>23</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13228,13 +13262,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13243,13 +13277,13 @@
         <v>25</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13258,13 +13292,13 @@
         <v>26</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13273,13 +13307,13 @@
         <v>27</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13288,13 +13322,13 @@
         <v>28</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13303,13 +13337,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13318,13 +13352,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13332,7 +13366,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -13345,13 +13379,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
@@ -13361,13 +13395,13 @@
         <v>3</v>
       </c>
       <c r="B40" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
@@ -13585,7 +13619,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -13598,13 +13632,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -13615,13 +13649,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -13632,13 +13666,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -13649,13 +13683,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -13666,13 +13700,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -13683,13 +13717,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -13700,13 +13734,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -13717,13 +13751,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -13734,13 +13768,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -13751,13 +13785,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -13768,13 +13802,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -13785,13 +13819,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -13802,13 +13836,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -13819,13 +13853,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -13836,13 +13870,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -13853,13 +13887,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -13870,13 +13904,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -13887,13 +13921,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -13904,13 +13938,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -13921,13 +13955,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -13938,13 +13972,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -13955,13 +13989,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -14021,22 +14055,22 @@
         <v>4</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H29" s="42" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14045,7 +14079,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>45729</v>
@@ -14081,7 +14115,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>45729</v>
@@ -14117,7 +14151,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="44" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>45729</v>
@@ -14153,7 +14187,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>45729</v>
@@ -14189,7 +14223,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C34" s="25" t="n">
         <v>45729</v>
@@ -14225,7 +14259,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C35" s="25" t="n">
         <v>45729</v>
@@ -14261,7 +14295,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C36" s="25" t="n">
         <v>45729</v>
@@ -14297,7 +14331,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C37" s="25" t="n">
         <v>45729</v>
@@ -14333,7 +14367,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C38" s="25" t="n">
         <v>45729</v>
@@ -14369,7 +14403,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C39" s="25" t="n">
         <v>45729</v>
@@ -14405,7 +14439,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C40" s="25" t="n">
         <v>45729</v>
@@ -14441,7 +14475,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C41" s="25" t="n">
         <v>45729</v>
@@ -14477,7 +14511,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C42" s="25" t="n">
         <v>45729</v>
@@ -14513,7 +14547,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C43" s="25" t="n">
         <v>45729</v>
@@ -14549,7 +14583,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="46" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C44" s="25" t="n">
         <v>45729</v>
@@ -14585,7 +14619,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="46" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C45" s="25" t="n">
         <v>45729</v>
@@ -14621,7 +14655,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="46" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C46" s="25" t="n">
         <v>45729</v>
@@ -14657,7 +14691,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="46" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C47" s="25" t="n">
         <v>45729</v>
@@ -14693,7 +14727,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="46" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C48" s="25" t="n">
         <v>45729</v>
@@ -14729,7 +14763,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="46" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C49" s="25" t="n">
         <v>45729</v>
@@ -14765,7 +14799,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C50" s="25" t="n">
         <v>45729</v>
@@ -14801,7 +14835,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C51" s="25" t="n">
         <v>45729</v>
@@ -14837,7 +14871,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="46" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C52" s="25" t="n">
         <v>45729</v>
@@ -14873,7 +14907,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="46" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C53" s="25" t="n">
         <v>45729</v>
@@ -15149,7 +15183,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q1" s="49" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="R1" s="49"/>
       <c r="S1" s="49"/>
@@ -15157,119 +15191,119 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q2" s="35" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R2" s="35" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="S2" s="35" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="T2" s="35" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q3" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q4" s="15" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q6" s="15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S6" s="15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="T6" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q7" s="15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S7" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q8" s="15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q9" s="15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="S9" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q12" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R12" s="50"/>
       <c r="S12" s="50"/>
@@ -15277,119 +15311,119 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q13" s="51" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R13" s="51" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="S13" s="51" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="T13" s="51" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q14" s="24" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q15" s="24" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="T15" s="24" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q16" s="24" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="T16" s="24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q17" s="24" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="T17" s="24" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q18" s="24" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="T18" s="24" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q19" s="24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R19" s="24" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="T19" s="24" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q20" s="24" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="R20" s="24" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="T20" s="24" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q23" s="50" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R23" s="50"/>
       <c r="S23" s="50"/>
@@ -15397,119 +15431,119 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q24" s="51" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R24" s="51" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="S24" s="51" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="T24" s="51" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q25" s="24" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="R25" s="24" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="S25" s="24" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="T25" s="24" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q26" s="24" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="S26" s="24" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="T26" s="24" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q27" s="24" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="R27" s="24" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="S27" s="24" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="T27" s="24" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q28" s="24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S28" s="24" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="T28" s="24" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q29" s="24" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="T29" s="24" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q30" s="24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R30" s="24" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S30" s="24" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T30" s="24" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q31" s="24" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="R31" s="24" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="S31" s="24" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T31" s="24" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q33" s="50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="R33" s="50"/>
       <c r="S33" s="50"/>
@@ -15517,154 +15551,154 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q34" s="51" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R34" s="51" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="S34" s="51" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="T34" s="51" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q35" s="24" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="R35" s="24" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="S35" s="24" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="T35" s="24" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q36" s="24" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="R36" s="24" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="S36" s="24" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="T36" s="24" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q37" s="24" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="R37" s="24" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="S37" s="24" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="T37" s="24" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q38" s="24" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="R38" s="24" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="S38" s="24" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="T38" s="24" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q39" s="24" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="R39" s="24" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="S39" s="24" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="T39" s="24" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q40" s="24" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="R40" s="24" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="S40" s="24" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="T40" s="24" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q41" s="24" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="R41" s="24" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="S41" s="24" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="T41" s="24" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="Q44" s="52" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="R44" s="52"/>
       <c r="S44" s="52"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q45" s="51" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R45" s="51" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="S45" s="51" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q46" s="24" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="R46" s="24" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="S46" s="24" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q47" s="24" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R47" s="24" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="S47" s="24" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -15701,291 +15735,291 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="53" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="54" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="54" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="54" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="54" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="54" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="54" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="53" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="54" t="s">
+        <v>415</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>416</v>
+      </c>
+      <c r="C13" s="54" t="s">
         <v>413</v>
       </c>
-      <c r="B13" s="54" t="s">
-        <v>414</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>411</v>
-      </c>
       <c r="D13" s="54" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="54" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C15" s="54" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D15" s="54" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D16" s="54" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="54" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D17" s="54" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="55" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="35" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C23" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C24" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C26" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -16019,13 +16053,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -16037,13 +16071,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E2" s="57" t="s">
         <v>14</v>
@@ -16055,13 +16089,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E3" s="57" t="s">
         <v>14</v>
@@ -16073,13 +16107,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>29</v>
@@ -16091,13 +16125,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E5" s="57" t="s">
         <v>14</v>
@@ -16109,13 +16143,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>29</v>
@@ -16127,13 +16161,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>29</v>
@@ -16145,13 +16179,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>29</v>
@@ -16163,13 +16197,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E9" s="57" t="s">
         <v>29</v>
@@ -16181,13 +16215,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E10" s="57" t="s">
         <v>14</v>
@@ -16199,13 +16233,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E11" s="57" t="s">
         <v>29</v>
@@ -16217,13 +16251,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E12" s="57" t="s">
         <v>29</v>
@@ -16235,13 +16269,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C13" s="56" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E13" s="57" t="s">
         <v>29</v>
@@ -16253,13 +16287,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E14" s="57" t="s">
         <v>14</v>
@@ -16271,13 +16305,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E15" s="57" t="s">
         <v>14</v>
@@ -16289,13 +16323,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E16" s="57" t="s">
         <v>14</v>
@@ -16307,13 +16341,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E17" s="57" t="s">
         <v>14</v>
@@ -16325,13 +16359,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>14</v>
@@ -16343,13 +16377,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E19" s="57" t="s">
         <v>29</v>
@@ -16361,13 +16395,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E20" s="57" t="s">
         <v>14</v>
@@ -16379,13 +16413,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C21" s="56" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E21" s="57" t="s">
         <v>29</v>
@@ -16397,13 +16431,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E22" s="57" t="s">
         <v>29</v>
@@ -16415,13 +16449,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E23" s="57" t="s">
         <v>29</v>
@@ -16433,13 +16467,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C24" s="56" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E24" s="57" t="s">
         <v>14</v>
@@ -16451,13 +16485,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E25" s="57" t="s">
         <v>14</v>
@@ -16469,13 +16503,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E26" s="57" t="s">
         <v>29</v>
@@ -16487,13 +16521,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C27" s="56" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E27" s="57" t="s">
         <v>14</v>
@@ -16505,16 +16539,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E28" s="57" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16523,16 +16557,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C29" s="56" t="s">
+        <v>509</v>
+      </c>
+      <c r="D29" s="56" t="s">
+        <v>510</v>
+      </c>
+      <c r="E29" s="57" t="s">
         <v>507</v>
-      </c>
-      <c r="D29" s="56" t="s">
-        <v>508</v>
-      </c>
-      <c r="E29" s="57" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16541,13 +16575,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E30" s="57" t="s">
         <v>29</v>
@@ -16559,13 +16593,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E31" s="57" t="s">
         <v>29</v>
@@ -16577,13 +16611,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E32" s="57" t="s">
         <v>29</v>
@@ -16595,13 +16629,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E33" s="57" t="s">
         <v>29</v>
@@ -16613,13 +16647,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C34" s="56" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E34" s="57" t="s">
         <v>29</v>
@@ -16631,13 +16665,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E35" s="57" t="s">
         <v>14</v>
@@ -16649,13 +16683,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C36" s="56" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E36" s="57" t="s">
         <v>29</v>
@@ -16667,13 +16701,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C37" s="56" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E37" s="57" t="s">
         <v>29</v>
@@ -16685,13 +16719,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C38" s="56" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E38" s="57" t="s">
         <v>29</v>
@@ -16703,13 +16737,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C39" s="56" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D39" s="56" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E39" s="57" t="s">
         <v>29</v>
@@ -16721,13 +16755,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C40" s="56" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D40" s="56" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E40" s="57" t="s">
         <v>29</v>
@@ -16739,13 +16773,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C41" s="56" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D41" s="56" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E41" s="57" t="s">
         <v>29</v>
@@ -16757,13 +16791,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="56" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C42" s="56" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D42" s="56" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E42" s="57" t="s">
         <v>29</v>
@@ -16775,16 +16809,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="56" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C43" s="56" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D43" s="56" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E43" s="57" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16793,13 +16827,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="56" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C44" s="56" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D44" s="56" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E44" s="57" t="s">
         <v>14</v>
@@ -16811,13 +16845,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="56" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C45" s="56" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D45" s="56" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E45" s="57" t="s">
         <v>14</v>
@@ -16829,13 +16863,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="56" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C46" s="56" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D46" s="56" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E46" s="57" t="s">
         <v>14</v>
@@ -16847,13 +16881,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="56" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C47" s="56" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D47" s="56" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E47" s="57" t="s">
         <v>29</v>
@@ -16865,13 +16899,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="56" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C48" s="56" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D48" s="56" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E48" s="57" t="s">
         <v>29</v>
@@ -16883,13 +16917,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="56" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C49" s="56" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D49" s="56" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E49" s="57" t="s">
         <v>29</v>
@@ -16898,13 +16932,13 @@
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>3</v>
@@ -16916,13 +16950,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>14</v>
@@ -16934,13 +16968,13 @@
         <v>2</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>14</v>
@@ -16952,13 +16986,13 @@
         <v>3</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>29</v>
@@ -16970,13 +17004,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>14</v>
@@ -16988,13 +17022,13 @@
         <v>5</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>29</v>
@@ -17006,13 +17040,13 @@
         <v>6</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>29</v>
@@ -17024,13 +17058,13 @@
         <v>7</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>29</v>
@@ -17042,13 +17076,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>14</v>
@@ -17060,13 +17094,13 @@
         <v>9</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>29</v>
@@ -17078,13 +17112,13 @@
         <v>10</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>29</v>
@@ -17096,13 +17130,13 @@
         <v>11</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>14</v>
@@ -17114,13 +17148,13 @@
         <v>12</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>14</v>
@@ -17132,13 +17166,13 @@
         <v>13</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>14</v>
@@ -17150,13 +17184,13 @@
         <v>14</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>14</v>
@@ -17168,13 +17202,13 @@
         <v>15</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>29</v>
@@ -17186,13 +17220,13 @@
         <v>16</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>14</v>
@@ -17204,13 +17238,13 @@
         <v>17</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>29</v>
@@ -17222,13 +17256,13 @@
         <v>18</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>29</v>
@@ -17240,13 +17274,13 @@
         <v>19</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>29</v>
@@ -17258,13 +17292,13 @@
         <v>20</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>14</v>
@@ -17276,13 +17310,13 @@
         <v>21</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>14</v>
@@ -17294,13 +17328,13 @@
         <v>22</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>14</v>
@@ -17312,13 +17346,13 @@
         <v>23</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>29</v>
@@ -17330,13 +17364,13 @@
         <v>24</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>14</v>
@@ -17348,16 +17382,16 @@
         <v>25</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17366,16 +17400,16 @@
         <v>26</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C77" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="E77" s="8" t="s">
         <v>507</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17384,13 +17418,13 @@
         <v>27</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>29</v>
@@ -17402,13 +17436,13 @@
         <v>28</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>29</v>
@@ -17420,13 +17454,13 @@
         <v>29</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>29</v>
@@ -17438,13 +17472,13 @@
         <v>30</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>29</v>
@@ -17456,13 +17490,13 @@
         <v>31</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>29</v>
@@ -17474,13 +17508,13 @@
         <v>32</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>29</v>
@@ -17492,16 +17526,16 @@
         <v>33</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17510,13 +17544,13 @@
         <v>34</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>29</v>
@@ -17528,13 +17562,13 @@
         <v>35</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>14</v>
@@ -17546,13 +17580,13 @@
         <v>36</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>29</v>
@@ -17564,13 +17598,13 @@
         <v>37</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>29</v>
@@ -17582,13 +17616,13 @@
         <v>38</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>29</v>
@@ -17600,13 +17634,13 @@
         <v>39</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>29</v>
@@ -17618,13 +17652,13 @@
         <v>40</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>29</v>
@@ -17636,13 +17670,13 @@
         <v>41</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>29</v>
@@ -17654,13 +17688,13 @@
         <v>42</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>29</v>
@@ -17672,13 +17706,13 @@
         <v>43</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>29</v>
@@ -17690,13 +17724,13 @@
         <v>44</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>29</v>
@@ -17708,16 +17742,16 @@
         <v>45</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>29</v>
@@ -17729,16 +17763,16 @@
         <v>46</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>29</v>
@@ -17750,16 +17784,16 @@
         <v>47</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>29</v>
@@ -17771,19 +17805,19 @@
         <v>48</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17792,16 +17826,16 @@
         <v>49</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>14</v>
@@ -17813,16 +17847,16 @@
         <v>50</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>14</v>
@@ -17833,22 +17867,22 @@
         <v>1</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H106" s="9"/>
     </row>
@@ -17858,22 +17892,22 @@
         <v>1</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17882,19 +17916,19 @@
         <v>2</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17903,19 +17937,19 @@
         <v>3</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17924,19 +17958,19 @@
         <v>4</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17948,19 +17982,19 @@
         <v>68</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17972,19 +18006,19 @@
         <v>68</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17996,16 +18030,16 @@
         <v>68</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18014,22 +18048,22 @@
         <v>8</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18038,19 +18072,19 @@
         <v>9</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18059,19 +18093,19 @@
         <v>10</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18080,22 +18114,22 @@
         <v>11</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18104,19 +18138,19 @@
         <v>12</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18125,19 +18159,19 @@
         <v>13</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18146,22 +18180,22 @@
         <v>14</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18170,19 +18204,19 @@
         <v>15</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18191,19 +18225,19 @@
         <v>16</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18212,22 +18246,22 @@
         <v>17</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>48</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18236,19 +18270,19 @@
         <v>18</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18257,19 +18291,19 @@
         <v>19</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18278,28 +18312,28 @@
         <v>20</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18308,19 +18342,19 @@
         <v>21</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18329,19 +18363,19 @@
         <v>22</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18350,25 +18384,25 @@
         <v>23</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>14</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18377,19 +18411,19 @@
         <v>24</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18398,19 +18432,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18419,22 +18453,22 @@
         <v>26</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18443,19 +18477,19 @@
         <v>27</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18464,19 +18498,19 @@
         <v>28</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18485,22 +18519,22 @@
         <v>29</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18509,19 +18543,19 @@
         <v>30</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18530,19 +18564,19 @@
         <v>31</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18551,19 +18585,19 @@
         <v>32</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18572,28 +18606,28 @@
         <v>33</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>29</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18602,19 +18636,19 @@
         <v>34</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18623,19 +18657,19 @@
         <v>35</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18644,25 +18678,25 @@
         <v>36</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18671,19 +18705,19 @@
         <v>37</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18692,19 +18726,19 @@
         <v>38</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18713,31 +18747,31 @@
         <v>39</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18746,19 +18780,19 @@
         <v>40</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18767,19 +18801,19 @@
         <v>41</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18788,19 +18822,19 @@
         <v>42</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18809,19 +18843,19 @@
         <v>43</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18830,22 +18864,22 @@
         <v>44</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18854,19 +18888,19 @@
         <v>45</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18875,19 +18909,19 @@
         <v>46</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18896,22 +18930,22 @@
         <v>47</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D153" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="F153" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="E153" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="F153" s="8" t="s">
-        <v>505</v>
-      </c>
       <c r="G153" s="8" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18920,19 +18954,19 @@
         <v>48</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18941,19 +18975,19 @@
         <v>49</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18962,22 +18996,22 @@
         <v>50</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18986,19 +19020,19 @@
         <v>51</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19007,19 +19041,19 @@
         <v>52</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19028,25 +19062,25 @@
         <v>53</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>29</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19055,19 +19089,19 @@
         <v>54</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19076,22 +19110,22 @@
         <v>55</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19100,19 +19134,19 @@
         <v>56</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19121,22 +19155,22 @@
         <v>57</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19145,22 +19179,22 @@
         <v>58</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19169,19 +19203,19 @@
         <v>59</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>
@@ -19223,28 +19257,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D1" s="42" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19253,10 +19287,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D2" s="59" t="n">
         <v>45849</v>
@@ -19292,10 +19326,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D3" s="59" t="n">
         <v>45849</v>
@@ -19331,10 +19365,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D4" s="59" t="n">
         <v>45849</v>
@@ -19370,10 +19404,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D5" s="61" t="n">
         <v>45849</v>
@@ -19409,10 +19443,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D6" s="61" t="n">
         <v>45849</v>
@@ -19448,10 +19482,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D7" s="61" t="n">
         <v>45849</v>
@@ -19487,10 +19521,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D8" s="61" t="n">
         <v>45849</v>
@@ -19526,10 +19560,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D9" s="62" t="n">
         <v>45850</v>
@@ -19565,10 +19599,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D10" s="62" t="n">
         <v>45850</v>
@@ -19604,10 +19638,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D11" s="62" t="n">
         <v>45850</v>
@@ -19643,7 +19677,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="62" t="n">
@@ -19680,10 +19714,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D13" s="62"/>
       <c r="E13" s="17" t="n">
@@ -19717,10 +19751,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D14" s="62" t="n">
         <v>45850</v>
@@ -19756,10 +19790,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D15" s="62" t="n">
         <v>45850</v>
@@ -19795,10 +19829,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D16" s="62" t="n">
         <v>45850</v>
@@ -19834,10 +19868,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D17" s="62"/>
       <c r="E17" s="17" t="n">
@@ -19871,10 +19905,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D18" s="62"/>
       <c r="E18" s="17" t="n">
@@ -19908,10 +19942,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D19" s="62"/>
       <c r="E19" s="17" t="n">
@@ -19945,10 +19979,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D20" s="62"/>
       <c r="E20" s="17" t="n">
@@ -19982,10 +20016,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D21" s="62"/>
       <c r="E21" s="17" t="n">
@@ -20019,10 +20053,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D22" s="62"/>
       <c r="E22" s="17" t="n">
@@ -20056,10 +20090,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D23" s="62"/>
       <c r="E23" s="17" t="n">
@@ -20093,10 +20127,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D24" s="62"/>
       <c r="E24" s="17" t="n">
@@ -20130,10 +20164,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D25" s="62"/>
       <c r="E25" s="17" t="n">
@@ -20167,10 +20201,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D26" s="62"/>
       <c r="E26" s="17" t="n">
@@ -20204,10 +20238,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D27" s="62"/>
       <c r="E27" s="17" t="n">
@@ -20244,7 +20278,7 @@
         <v>67</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D28" s="62"/>
       <c r="E28" s="17" t="n">
@@ -20278,10 +20312,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D29" s="62"/>
       <c r="E29" s="17" t="n">
@@ -20315,10 +20349,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D30" s="62"/>
       <c r="E30" s="17" t="n">
@@ -20352,10 +20386,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D31" s="62"/>
       <c r="E31" s="17" t="n">
@@ -20389,10 +20423,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D32" s="62"/>
       <c r="E32" s="17" t="n">
@@ -20426,10 +20460,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D33" s="62"/>
       <c r="E33" s="17" t="n">
@@ -20463,10 +20497,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D34" s="62"/>
       <c r="E34" s="17" t="n">
@@ -20500,10 +20534,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D35" s="62"/>
       <c r="E35" s="17" t="n">
@@ -20537,10 +20571,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D36" s="62"/>
       <c r="E36" s="17" t="n">
@@ -20574,10 +20608,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D37" s="62"/>
       <c r="E37" s="17" t="n">
@@ -20614,7 +20648,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D38" s="62"/>
       <c r="E38" s="17" t="n">
@@ -20648,10 +20682,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D39" s="62"/>
       <c r="E39" s="17" t="n">
@@ -20685,10 +20719,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D40" s="62"/>
       <c r="E40" s="17" t="n">
@@ -20722,10 +20756,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D41" s="62"/>
       <c r="E41" s="17" t="n">
@@ -20759,7 +20793,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="62"/>
@@ -20794,7 +20828,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="62"/>
@@ -20829,7 +20863,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="62"/>
@@ -20864,10 +20898,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="17" t="n">
@@ -20901,10 +20935,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D46" s="62"/>
       <c r="E46" s="17" t="n">
@@ -20938,10 +20972,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D47" s="62"/>
       <c r="E47" s="17" t="n">
@@ -20975,10 +21009,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D48" s="62"/>
       <c r="E48" s="17" t="n">
@@ -21012,10 +21046,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D49" s="62"/>
       <c r="E49" s="17" t="n">
@@ -21049,10 +21083,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D50" s="62"/>
       <c r="E50" s="17" t="n">
@@ -21086,10 +21120,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D51" s="62"/>
       <c r="E51" s="17" t="n">
@@ -21123,10 +21157,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D52" s="62"/>
       <c r="E52" s="17" t="n">
@@ -21160,10 +21194,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D53" s="62"/>
       <c r="E53" s="17" t="n">
@@ -21197,10 +21231,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D54" s="62"/>
       <c r="E54" s="17" t="n">
@@ -21234,10 +21268,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="D55" s="62"/>
       <c r="E55" s="17" t="n">
@@ -21271,10 +21305,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D56" s="62"/>
       <c r="E56" s="17" t="n">
@@ -21308,10 +21342,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D57" s="62"/>
       <c r="E57" s="17" t="n">
@@ -21345,10 +21379,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D58" s="62"/>
       <c r="E58" s="17" t="n">
@@ -21382,10 +21416,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D59" s="62"/>
       <c r="E59" s="17" t="n">
@@ -21419,7 +21453,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C60" s="16"/>
       <c r="D60" s="62"/>
@@ -21454,10 +21488,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D61" s="62"/>
       <c r="E61" s="17" t="n">
@@ -21491,10 +21525,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D62" s="62"/>
       <c r="E62" s="17" t="n">
@@ -21528,10 +21562,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D63" s="62"/>
       <c r="E63" s="17" t="n">
@@ -21565,10 +21599,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D64" s="62"/>
       <c r="E64" s="17" t="n">
@@ -21602,10 +21636,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D65" s="62"/>
       <c r="E65" s="17" t="n">
@@ -21639,10 +21673,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D66" s="62"/>
       <c r="E66" s="17" t="n">
@@ -21676,10 +21710,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="65" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D67" s="62"/>
       <c r="E67" s="17"/>
@@ -21695,10 +21729,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="65" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D68" s="62"/>
       <c r="E68" s="17"/>
@@ -21714,10 +21748,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="65" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D69" s="62"/>
       <c r="E69" s="17"/>
@@ -21733,10 +21767,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D70" s="62"/>
       <c r="E70" s="17"/>
@@ -21752,10 +21786,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="65" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D71" s="62"/>
       <c r="E71" s="17"/>
@@ -26073,10 +26107,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="68" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
@@ -26088,10 +26122,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="70" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C2" s="71"/>
       <c r="D2" s="71"/>
@@ -26103,10 +26137,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="70" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C3" s="71"/>
       <c r="D3" s="71"/>
@@ -26118,10 +26152,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="70" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
@@ -26133,10 +26167,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="70" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
@@ -26148,10 +26182,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="70" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
@@ -26163,10 +26197,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="70" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
@@ -26178,16 +26212,16 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="70" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C8" s="71"/>
       <c r="D8" s="71"/>
       <c r="E8" s="71"/>
       <c r="F8" s="11" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="G8" s="69"/>
       <c r="H8" s="69"/>
@@ -26206,7 +26240,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C10" s="42" t="s">
         <v>4</v>
@@ -26227,7 +26261,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="72" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26236,7 +26270,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="73" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C11" s="17" t="n">
         <v>45855</v>
@@ -26272,7 +26306,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="74" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C12" s="17" t="n">
         <v>45855</v>
@@ -26309,7 +26343,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="74" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C13" s="75"/>
       <c r="D13" s="17"/>
